--- a/research/traditional_assets/database/data/macau/macau_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_telecom_equipment.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0307</v>
-      </c>
-      <c r="E2">
-        <v>-0.108</v>
+        <v>0.0241</v>
       </c>
       <c r="G2">
-        <v>-0.01720292504570384</v>
+        <v>-0.005263929618768328</v>
       </c>
       <c r="H2">
-        <v>-0.01720292504570384</v>
+        <v>-0.005263929618768328</v>
       </c>
       <c r="I2">
-        <v>-0.005758683729433272</v>
+        <v>-0.02624633431085044</v>
       </c>
       <c r="J2">
-        <v>-0.005525594149908592</v>
+        <v>-0.02624633431085044</v>
       </c>
       <c r="K2">
-        <v>1.08</v>
+        <v>-1.29</v>
       </c>
       <c r="L2">
-        <v>0.01974405850091408</v>
+        <v>-0.0189149560117302</v>
       </c>
       <c r="M2">
         <v>0.6161</v>
       </c>
       <c r="N2">
-        <v>0.05357391304347826</v>
+        <v>0.05867619047619047</v>
       </c>
       <c r="O2">
-        <v>0.5704629629629629</v>
+        <v>-0.4775968992248062</v>
       </c>
       <c r="P2">
         <v>0.6161</v>
       </c>
       <c r="Q2">
-        <v>0.05357391304347826</v>
+        <v>0.05867619047619047</v>
       </c>
       <c r="R2">
-        <v>0.5704629629629629</v>
+        <v>-0.4775968992248062</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,52 +639,52 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1210022161839512</v>
+        <v>0.1040169585400613</v>
       </c>
       <c r="AB2">
-        <v>0.1205675056449895</v>
+        <v>0.1026321802054318</v>
       </c>
       <c r="AD2">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AG2">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AH2">
-        <v>0.005964214711729622</v>
+        <v>0.02088772845953003</v>
       </c>
       <c r="AI2">
-        <v>0.003259483206575653</v>
+        <v>0.008951406649616368</v>
       </c>
       <c r="AJ2">
-        <v>0.005964214711729622</v>
+        <v>0.02088772845953003</v>
       </c>
       <c r="AK2">
-        <v>0.003259483206575653</v>
+        <v>0.008951406649616368</v>
       </c>
       <c r="AL2">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="AM2">
-        <v>-0.413</v>
+        <v>-0.424</v>
       </c>
       <c r="AN2">
-        <v>-0.3122171945701357</v>
+        <v>-0.1325443786982249</v>
       </c>
       <c r="AO2">
-        <v>-26.25</v>
+        <v>-119.3333333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.3122171945701357</v>
+        <v>-0.1325443786982249</v>
       </c>
       <c r="AQ2">
-        <v>0.7627118644067797</v>
+        <v>4.221698113207547</v>
       </c>
     </row>
     <row r="3">
@@ -707,46 +704,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0307</v>
-      </c>
-      <c r="E3">
-        <v>-0.108</v>
+        <v>0.0241</v>
       </c>
       <c r="G3">
-        <v>-0.01720292504570384</v>
+        <v>-0.005263929618768328</v>
       </c>
       <c r="H3">
-        <v>-0.01720292504570384</v>
+        <v>-0.005263929618768328</v>
       </c>
       <c r="I3">
-        <v>-0.005758683729433272</v>
+        <v>-0.02624633431085044</v>
       </c>
       <c r="J3">
-        <v>-0.005525594149908592</v>
+        <v>-0.02624633431085044</v>
       </c>
       <c r="K3">
-        <v>1.08</v>
+        <v>-1.29</v>
       </c>
       <c r="L3">
-        <v>0.01974405850091408</v>
+        <v>-0.0189149560117302</v>
       </c>
       <c r="M3">
         <v>0.6161</v>
       </c>
       <c r="N3">
-        <v>0.05357391304347826</v>
+        <v>0.05867619047619047</v>
       </c>
       <c r="O3">
-        <v>0.5704629629629629</v>
+        <v>-0.4775968992248062</v>
       </c>
       <c r="P3">
         <v>0.6161</v>
       </c>
       <c r="Q3">
-        <v>0.05357391304347826</v>
+        <v>0.05867619047619047</v>
       </c>
       <c r="R3">
-        <v>0.5704629629629629</v>
+        <v>-0.4775968992248062</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,52 +755,52 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1210022161839512</v>
+        <v>0.1040169585400613</v>
       </c>
       <c r="AB3">
-        <v>0.1205675056449895</v>
+        <v>0.1026321802054318</v>
       </c>
       <c r="AD3">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AG3">
-        <v>0.06900000000000001</v>
+        <v>0.224</v>
       </c>
       <c r="AH3">
-        <v>0.005964214711729622</v>
+        <v>0.02088772845953003</v>
       </c>
       <c r="AI3">
-        <v>0.003259483206575653</v>
+        <v>0.008951406649616368</v>
       </c>
       <c r="AJ3">
-        <v>0.005964214711729622</v>
+        <v>0.02088772845953003</v>
       </c>
       <c r="AK3">
-        <v>0.003259483206575653</v>
+        <v>0.008951406649616368</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="AM3">
-        <v>-0.413</v>
+        <v>-0.424</v>
       </c>
       <c r="AN3">
-        <v>-0.3122171945701357</v>
+        <v>-0.1325443786982249</v>
       </c>
       <c r="AO3">
-        <v>-26.25</v>
+        <v>-119.3333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.3122171945701357</v>
+        <v>-0.1325443786982249</v>
       </c>
       <c r="AQ3">
-        <v>0.7627118644067797</v>
+        <v>4.221698113207547</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/macau/macau_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_telecom_equipment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059545037396958</v>
+        <v>0.1057028229426509</v>
       </c>
       <c r="C2">
-        <v>13.74458382569298</v>
+        <v>13.61621555366568</v>
       </c>
       <c r="D2">
-        <v>8.264583825692984</v>
+        <v>8.277215553665682</v>
       </c>
       <c r="E2">
-        <v>-6.25</v>
+        <v>-6.109</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
         <v>5.48</v>
@@ -1445,28 +1445,28 @@
         <v>2.21</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007092299999999999</v>
       </c>
       <c r="N2">
-        <v>2.21</v>
+        <v>2.2029077</v>
       </c>
       <c r="O2">
-        <v>0.593606</v>
+        <v>0.5917010082199999</v>
       </c>
       <c r="P2">
-        <v>1.616394</v>
+        <v>1.61120669178</v>
       </c>
       <c r="Q2">
-        <v>1.746394</v>
+        <v>1.74120669178</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059545037396958</v>
+        <v>0.1063989179218696</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181185703003852</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>311.6055440407202</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1057028229426509</v>
+        <v>0.1054511421456061</v>
       </c>
       <c r="C3">
-        <v>13.61621555366568</v>
+        <v>13.48788595383368</v>
       </c>
       <c r="D3">
-        <v>8.277215553665682</v>
+        <v>8.289885953833682</v>
       </c>
       <c r="E3">
-        <v>-6.109</v>
+        <v>-5.968</v>
       </c>
       <c r="F3">
-        <v>0.141</v>
+        <v>0.282</v>
       </c>
       <c r="G3">
         <v>5.48</v>
@@ -1527,28 +1527,28 @@
         <v>2.21</v>
       </c>
       <c r="M3">
-        <v>0.007092299999999999</v>
+        <v>0.0141846</v>
       </c>
       <c r="N3">
-        <v>2.2029077</v>
+        <v>2.1958154</v>
       </c>
       <c r="O3">
-        <v>0.5917010082199999</v>
+        <v>0.58979601644</v>
       </c>
       <c r="P3">
-        <v>1.61120669178</v>
+        <v>1.60601938356</v>
       </c>
       <c r="Q3">
-        <v>1.74120669178</v>
+        <v>1.73601938356</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1063989179218696</v>
+        <v>0.1068524017812307</v>
       </c>
       <c r="T3">
-        <v>1.181185703003852</v>
+        <v>1.190024947491864</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>311.6055440407202</v>
+        <v>155.8027720203601</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1054511421456061</v>
+        <v>0.1051994613485613</v>
       </c>
       <c r="C4">
-        <v>13.48788595383368</v>
+        <v>13.35959520406238</v>
       </c>
       <c r="D4">
-        <v>8.289885953833682</v>
+        <v>8.302595204062376</v>
       </c>
       <c r="E4">
-        <v>-5.968</v>
+        <v>-5.827</v>
       </c>
       <c r="F4">
-        <v>0.282</v>
+        <v>0.423</v>
       </c>
       <c r="G4">
         <v>5.48</v>
@@ -1609,28 +1609,28 @@
         <v>2.21</v>
       </c>
       <c r="M4">
-        <v>0.0141846</v>
+        <v>0.0212769</v>
       </c>
       <c r="N4">
-        <v>2.1958154</v>
+        <v>2.1887231</v>
       </c>
       <c r="O4">
-        <v>0.58979601644</v>
+        <v>0.58789102466</v>
       </c>
       <c r="P4">
-        <v>1.60601938356</v>
+        <v>1.60083207534</v>
       </c>
       <c r="Q4">
-        <v>1.73601938356</v>
+        <v>1.73083207534</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1068524017812307</v>
+        <v>0.1073152358232591</v>
       </c>
       <c r="T4">
-        <v>1.190024947491864</v>
+        <v>1.199046444443546</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.8027720203601</v>
+        <v>103.8685146802401</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1051994613485613</v>
+        <v>0.1049477805515165</v>
       </c>
       <c r="C5">
-        <v>13.35959520406238</v>
+        <v>13.23134348330958</v>
       </c>
       <c r="D5">
-        <v>8.302595204062376</v>
+        <v>8.315343483309579</v>
       </c>
       <c r="E5">
-        <v>-5.827</v>
+        <v>-5.686</v>
       </c>
       <c r="F5">
-        <v>0.423</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G5">
         <v>5.48</v>
@@ -1691,28 +1691,28 @@
         <v>2.21</v>
       </c>
       <c r="M5">
-        <v>0.0212769</v>
+        <v>0.0283692</v>
       </c>
       <c r="N5">
-        <v>2.1887231</v>
+        <v>2.1816308</v>
       </c>
       <c r="O5">
-        <v>0.58789102466</v>
+        <v>0.58598603288</v>
       </c>
       <c r="P5">
-        <v>1.60083207534</v>
+        <v>1.59564476712</v>
       </c>
       <c r="Q5">
-        <v>1.73083207534</v>
+        <v>1.72564476712</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1073152358232591</v>
+        <v>0.107787712241163</v>
       </c>
       <c r="T5">
-        <v>1.199046444443546</v>
+        <v>1.208255889248387</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.8685146802401</v>
+        <v>77.90138601018005</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1049477805515165</v>
+        <v>0.1046960997544716</v>
       </c>
       <c r="C6">
-        <v>13.23134348330958</v>
+        <v>13.10313097163392</v>
       </c>
       <c r="D6">
-        <v>8.315343483309579</v>
+        <v>8.32813097163392</v>
       </c>
       <c r="E6">
-        <v>-5.686</v>
+        <v>-5.545</v>
       </c>
       <c r="F6">
-        <v>0.5639999999999999</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="G6">
         <v>5.48</v>
@@ -1773,28 +1773,28 @@
         <v>2.21</v>
       </c>
       <c r="M6">
-        <v>0.0283692</v>
+        <v>0.0354615</v>
       </c>
       <c r="N6">
-        <v>2.1816308</v>
+        <v>2.1745385</v>
       </c>
       <c r="O6">
-        <v>0.58598603288</v>
+        <v>0.5840810411</v>
       </c>
       <c r="P6">
-        <v>1.59564476712</v>
+        <v>1.5904574589</v>
       </c>
       <c r="Q6">
-        <v>1.72564476712</v>
+        <v>1.7204574589</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.107787712241163</v>
+        <v>0.1082701355310228</v>
       </c>
       <c r="T6">
-        <v>1.208255889248387</v>
+        <v>1.217659217101752</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.90138601018005</v>
+        <v>62.32110880814405</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1046960997544716</v>
+        <v>0.1044444189574268</v>
       </c>
       <c r="C7">
-        <v>13.10313097163392</v>
+        <v>12.97495785020332</v>
       </c>
       <c r="D7">
-        <v>8.32813097163392</v>
+        <v>8.340957850203322</v>
       </c>
       <c r="E7">
-        <v>-5.545</v>
+        <v>-5.404</v>
       </c>
       <c r="F7">
-        <v>0.7050000000000001</v>
+        <v>0.8460000000000001</v>
       </c>
       <c r="G7">
         <v>5.48</v>
@@ -1855,28 +1855,28 @@
         <v>2.21</v>
       </c>
       <c r="M7">
-        <v>0.0354615</v>
+        <v>0.0425538</v>
       </c>
       <c r="N7">
-        <v>2.1745385</v>
+        <v>2.1674462</v>
       </c>
       <c r="O7">
-        <v>0.5840810411</v>
+        <v>0.58217604932</v>
       </c>
       <c r="P7">
-        <v>1.5904574589</v>
+        <v>1.58527015068</v>
       </c>
       <c r="Q7">
-        <v>1.7204574589</v>
+        <v>1.71527015068</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1082701355310228</v>
+        <v>0.1087628231461987</v>
       </c>
       <c r="T7">
-        <v>1.217659217101752</v>
+        <v>1.227262615760507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.32110880814405</v>
+        <v>51.93425734012003</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1044444189574268</v>
+        <v>0.104192738160382</v>
       </c>
       <c r="C8">
-        <v>12.97495785020332</v>
+        <v>12.84682430130357</v>
       </c>
       <c r="D8">
-        <v>8.340957850203322</v>
+        <v>8.353824301303565</v>
       </c>
       <c r="E8">
-        <v>-5.404</v>
+        <v>-5.263</v>
       </c>
       <c r="F8">
-        <v>0.846</v>
+        <v>0.9869999999999999</v>
       </c>
       <c r="G8">
         <v>5.48</v>
@@ -1937,28 +1937,28 @@
         <v>2.21</v>
       </c>
       <c r="M8">
-        <v>0.0425538</v>
+        <v>0.04964609999999999</v>
       </c>
       <c r="N8">
-        <v>2.1674462</v>
+        <v>2.1603539</v>
       </c>
       <c r="O8">
-        <v>0.58217604932</v>
+        <v>0.5802710575400001</v>
       </c>
       <c r="P8">
-        <v>1.58527015068</v>
+        <v>1.58008284246</v>
       </c>
       <c r="Q8">
-        <v>1.71527015068</v>
+        <v>1.71008284246</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1087628231461987</v>
+        <v>0.1092661061939591</v>
       </c>
       <c r="T8">
-        <v>1.227262615760507</v>
+        <v>1.237072539121601</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.93425734012004</v>
+        <v>44.51507772010289</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.104192738160382</v>
+        <v>0.1039410573633372</v>
       </c>
       <c r="C9">
-        <v>12.84682430130357</v>
+        <v>12.71873050834691</v>
       </c>
       <c r="D9">
-        <v>8.353824301303565</v>
+        <v>8.36673050834691</v>
       </c>
       <c r="E9">
-        <v>-5.263</v>
+        <v>-5.122</v>
       </c>
       <c r="F9">
-        <v>0.9870000000000001</v>
+        <v>1.128</v>
       </c>
       <c r="G9">
         <v>5.48</v>
@@ -2019,28 +2019,28 @@
         <v>2.21</v>
       </c>
       <c r="M9">
-        <v>0.04964610000000001</v>
+        <v>0.05673839999999999</v>
       </c>
       <c r="N9">
-        <v>2.1603539</v>
+        <v>2.1532616</v>
       </c>
       <c r="O9">
-        <v>0.5802710575400001</v>
+        <v>0.57836606576</v>
       </c>
       <c r="P9">
-        <v>1.58008284246</v>
+        <v>1.57489553424</v>
       </c>
       <c r="Q9">
-        <v>1.71008284246</v>
+        <v>1.70489553424</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1092661061939591</v>
+        <v>0.1097803301775404</v>
       </c>
       <c r="T9">
-        <v>1.237072539121602</v>
+        <v>1.247095721686198</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.51507772010289</v>
+        <v>38.95069300509003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1039410573633372</v>
+        <v>0.1036893765662923</v>
       </c>
       <c r="C10">
-        <v>12.71873050834691</v>
+        <v>12.59067665588083</v>
       </c>
       <c r="D10">
-        <v>8.36673050834691</v>
+        <v>8.379676655880829</v>
       </c>
       <c r="E10">
-        <v>-5.122</v>
+        <v>-4.981</v>
       </c>
       <c r="F10">
-        <v>1.128</v>
+        <v>1.269</v>
       </c>
       <c r="G10">
         <v>5.48</v>
@@ -2101,28 +2101,28 @@
         <v>2.21</v>
       </c>
       <c r="M10">
-        <v>0.05673839999999999</v>
+        <v>0.06383069999999999</v>
       </c>
       <c r="N10">
-        <v>2.1532616</v>
+        <v>2.1461693</v>
       </c>
       <c r="O10">
-        <v>0.57836606576</v>
+        <v>0.57646107398</v>
       </c>
       <c r="P10">
-        <v>1.57489553424</v>
+        <v>1.56970822602</v>
       </c>
       <c r="Q10">
-        <v>1.70489553424</v>
+        <v>1.69970822602</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1097803301775404</v>
+        <v>0.1103058557871344</v>
       </c>
       <c r="T10">
-        <v>1.247095721686198</v>
+        <v>1.257339193977488</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.95069300509003</v>
+        <v>34.62283822674669</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1036893765662923</v>
+        <v>0.1034376957692475</v>
       </c>
       <c r="C11">
-        <v>12.59067665588083</v>
+        <v>12.46266292959678</v>
       </c>
       <c r="D11">
-        <v>8.379676655880829</v>
+        <v>8.39266292959678</v>
       </c>
       <c r="E11">
-        <v>-4.981</v>
+        <v>-4.84</v>
       </c>
       <c r="F11">
-        <v>1.269</v>
+        <v>1.41</v>
       </c>
       <c r="G11">
         <v>5.48</v>
@@ -2183,28 +2183,28 @@
         <v>2.21</v>
       </c>
       <c r="M11">
-        <v>0.06383069999999999</v>
+        <v>0.07092299999999999</v>
       </c>
       <c r="N11">
-        <v>2.1461693</v>
+        <v>2.139077</v>
       </c>
       <c r="O11">
-        <v>0.57646107398</v>
+        <v>0.5745560822</v>
       </c>
       <c r="P11">
-        <v>1.56970822602</v>
+        <v>1.5645209178</v>
       </c>
       <c r="Q11">
-        <v>1.69970822602</v>
+        <v>1.6945209178</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1103058557871344</v>
+        <v>0.1108430597436084</v>
       </c>
       <c r="T11">
-        <v>1.257339193977488</v>
+        <v>1.267810298986363</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.62283822674669</v>
+        <v>31.16055440407203</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1034376957692475</v>
+        <v>0.1031860149722027</v>
       </c>
       <c r="C12">
-        <v>12.46266292959678</v>
+        <v>12.33468951633911</v>
       </c>
       <c r="D12">
-        <v>8.39266292959678</v>
+        <v>8.405689516339105</v>
       </c>
       <c r="E12">
-        <v>-4.84</v>
+        <v>-4.699</v>
       </c>
       <c r="F12">
-        <v>1.41</v>
+        <v>1.551</v>
       </c>
       <c r="G12">
         <v>5.48</v>
@@ -2265,28 +2265,28 @@
         <v>2.21</v>
       </c>
       <c r="M12">
-        <v>0.070923</v>
+        <v>0.0780153</v>
       </c>
       <c r="N12">
-        <v>2.139077</v>
+        <v>2.1319847</v>
       </c>
       <c r="O12">
-        <v>0.5745560822</v>
+        <v>0.57265109042</v>
       </c>
       <c r="P12">
-        <v>1.5645209178</v>
+        <v>1.55933360958</v>
       </c>
       <c r="Q12">
-        <v>1.6945209178</v>
+        <v>1.68933360958</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1108430597436084</v>
+        <v>0.1113923356991042</v>
       </c>
       <c r="T12">
-        <v>1.267810298986363</v>
+        <v>1.278516709725775</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.16055440407202</v>
+        <v>28.32777673097457</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1031860149722027</v>
+        <v>0.1029343341751579</v>
       </c>
       <c r="C13">
-        <v>12.33468951633911</v>
+        <v>12.20675660411399</v>
       </c>
       <c r="D13">
-        <v>8.405689516339105</v>
+        <v>8.418756604113989</v>
       </c>
       <c r="E13">
-        <v>-4.699</v>
+        <v>-4.558</v>
       </c>
       <c r="F13">
-        <v>1.551</v>
+        <v>1.692</v>
       </c>
       <c r="G13">
         <v>5.48</v>
@@ -2347,28 +2347,28 @@
         <v>2.21</v>
       </c>
       <c r="M13">
-        <v>0.0780153</v>
+        <v>0.08510759999999999</v>
       </c>
       <c r="N13">
-        <v>2.1319847</v>
+        <v>2.1248924</v>
       </c>
       <c r="O13">
-        <v>0.57265109042</v>
+        <v>0.5707460986399999</v>
       </c>
       <c r="P13">
-        <v>1.55933360958</v>
+        <v>1.55414630136</v>
       </c>
       <c r="Q13">
-        <v>1.68933360958</v>
+        <v>1.68414630136</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1113923356991042</v>
+        <v>0.111954095199043</v>
       </c>
       <c r="T13">
-        <v>1.278516709725775</v>
+        <v>1.289466447981991</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.32777673097457</v>
+        <v>25.96712867006002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1029343341751579</v>
+        <v>0.1026826533781131</v>
       </c>
       <c r="C14">
-        <v>12.20675660411399</v>
+        <v>12.07886438209848</v>
       </c>
       <c r="D14">
-        <v>8.418756604113989</v>
+        <v>8.431864382098482</v>
       </c>
       <c r="E14">
-        <v>-4.558</v>
+        <v>-4.417</v>
       </c>
       <c r="F14">
-        <v>1.692</v>
+        <v>1.833</v>
       </c>
       <c r="G14">
         <v>5.48</v>
@@ -2429,28 +2429,28 @@
         <v>2.21</v>
       </c>
       <c r="M14">
-        <v>0.08510759999999999</v>
+        <v>0.09219989999999999</v>
       </c>
       <c r="N14">
-        <v>2.1248924</v>
+        <v>2.1178001</v>
       </c>
       <c r="O14">
-        <v>0.5707460986399999</v>
+        <v>0.5688411068600001</v>
       </c>
       <c r="P14">
-        <v>1.55414630136</v>
+        <v>1.54895899314</v>
       </c>
       <c r="Q14">
-        <v>1.68414630136</v>
+        <v>1.67895899314</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.111954095199043</v>
+        <v>0.1125287687104748</v>
       </c>
       <c r="T14">
-        <v>1.289466447981991</v>
+        <v>1.30066790435904</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.96712867006002</v>
+        <v>23.96965723390156</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1026826533781131</v>
+        <v>0.1024309725810682</v>
       </c>
       <c r="C15">
-        <v>12.07886438209848</v>
+        <v>11.95101304064966</v>
       </c>
       <c r="D15">
-        <v>8.431864382098482</v>
+        <v>8.445013040649664</v>
       </c>
       <c r="E15">
-        <v>-4.417</v>
+        <v>-4.276</v>
       </c>
       <c r="F15">
-        <v>1.833</v>
+        <v>1.974</v>
       </c>
       <c r="G15">
         <v>5.48</v>
@@ -2511,28 +2511,28 @@
         <v>2.21</v>
       </c>
       <c r="M15">
-        <v>0.09219989999999999</v>
+        <v>0.09929220000000001</v>
       </c>
       <c r="N15">
-        <v>2.1178001</v>
+        <v>2.1107078</v>
       </c>
       <c r="O15">
-        <v>0.5688411068600001</v>
+        <v>0.5669361150800001</v>
       </c>
       <c r="P15">
-        <v>1.54895899314</v>
+        <v>1.54377168492</v>
       </c>
       <c r="Q15">
-        <v>1.67895899314</v>
+        <v>1.67377168492</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1125287687104748</v>
+        <v>0.1131168067221724</v>
       </c>
       <c r="T15">
-        <v>1.30066790435904</v>
+        <v>1.312129859721601</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.96965723390156</v>
+        <v>22.25753886005144</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1024309725810682</v>
+        <v>0.1021792917840234</v>
       </c>
       <c r="C16">
-        <v>11.95101304064966</v>
+        <v>11.82320277131383</v>
       </c>
       <c r="D16">
-        <v>8.445013040649664</v>
+        <v>8.458202771313832</v>
       </c>
       <c r="E16">
-        <v>-4.276</v>
+        <v>-4.135</v>
       </c>
       <c r="F16">
-        <v>1.974</v>
+        <v>2.115</v>
       </c>
       <c r="G16">
         <v>5.48</v>
@@ -2593,28 +2593,28 @@
         <v>2.21</v>
       </c>
       <c r="M16">
-        <v>0.09929220000000001</v>
+        <v>0.1063845</v>
       </c>
       <c r="N16">
-        <v>2.1107078</v>
+        <v>2.1036155</v>
       </c>
       <c r="O16">
-        <v>0.5669361150800001</v>
+        <v>0.5650311233</v>
       </c>
       <c r="P16">
-        <v>1.54377168492</v>
+        <v>1.5385843767</v>
       </c>
       <c r="Q16">
-        <v>1.67377168492</v>
+        <v>1.6685843767</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1131168067221724</v>
+        <v>0.1137186809223805</v>
       </c>
       <c r="T16">
-        <v>1.312129859721601</v>
+        <v>1.323861508151517</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.25753886005144</v>
+        <v>20.77370293604801</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1021792917840234</v>
+        <v>0.1019276109869786</v>
       </c>
       <c r="C17">
-        <v>11.82320277131383</v>
+        <v>11.69543376683581</v>
       </c>
       <c r="D17">
-        <v>8.458202771313834</v>
+        <v>8.471433766835814</v>
       </c>
       <c r="E17">
-        <v>-4.135</v>
+        <v>-3.994</v>
       </c>
       <c r="F17">
-        <v>2.115</v>
+        <v>2.256</v>
       </c>
       <c r="G17">
         <v>5.48</v>
@@ -2675,28 +2675,28 @@
         <v>2.21</v>
       </c>
       <c r="M17">
-        <v>0.1063845</v>
+        <v>0.1134768</v>
       </c>
       <c r="N17">
-        <v>2.1036155</v>
+        <v>2.0965232</v>
       </c>
       <c r="O17">
-        <v>0.5650311233</v>
+        <v>0.56312613152</v>
       </c>
       <c r="P17">
-        <v>1.5385843767</v>
+        <v>1.53339706848</v>
       </c>
       <c r="Q17">
-        <v>1.6685843767</v>
+        <v>1.66339706848</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1137186809223805</v>
+        <v>0.1143348854606888</v>
       </c>
       <c r="T17">
-        <v>1.323861508151517</v>
+        <v>1.33587248154405</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.77370293604802</v>
+        <v>19.47534650254502</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1019276109869786</v>
+        <v>0.1016759301899338</v>
       </c>
       <c r="C18">
-        <v>11.69543376683581</v>
+        <v>11.56770622116835</v>
       </c>
       <c r="D18">
-        <v>8.471433766835814</v>
+        <v>8.48470622116835</v>
       </c>
       <c r="E18">
-        <v>-3.994</v>
+        <v>-3.853</v>
       </c>
       <c r="F18">
-        <v>2.256</v>
+        <v>2.397</v>
       </c>
       <c r="G18">
         <v>5.48</v>
@@ -2757,28 +2757,28 @@
         <v>2.21</v>
       </c>
       <c r="M18">
-        <v>0.1134768</v>
+        <v>0.1205691</v>
       </c>
       <c r="N18">
-        <v>2.0965232</v>
+        <v>2.0894309</v>
       </c>
       <c r="O18">
-        <v>0.56312613152</v>
+        <v>0.56122113974</v>
       </c>
       <c r="P18">
-        <v>1.53339706848</v>
+        <v>1.52820976026</v>
       </c>
       <c r="Q18">
-        <v>1.66339706848</v>
+        <v>1.65820976026</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1143348854606888</v>
+        <v>0.114965938301125</v>
       </c>
       <c r="T18">
-        <v>1.33587248154405</v>
+        <v>1.348172875982186</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.47534650254502</v>
+        <v>18.32973788474825</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1016759301899338</v>
+        <v>0.1014242493928889</v>
       </c>
       <c r="C19">
-        <v>11.56770622116835</v>
+        <v>11.44002032948158</v>
       </c>
       <c r="D19">
-        <v>8.48470622116835</v>
+        <v>8.49802032948158</v>
       </c>
       <c r="E19">
-        <v>-3.853</v>
+        <v>-3.712</v>
       </c>
       <c r="F19">
-        <v>2.397</v>
+        <v>2.538</v>
       </c>
       <c r="G19">
         <v>5.48</v>
@@ -2839,28 +2839,28 @@
         <v>2.21</v>
       </c>
       <c r="M19">
-        <v>0.1205691</v>
+        <v>0.1276614</v>
       </c>
       <c r="N19">
-        <v>2.0894309</v>
+        <v>2.0823386</v>
       </c>
       <c r="O19">
-        <v>0.56122113974</v>
+        <v>0.55931614796</v>
       </c>
       <c r="P19">
-        <v>1.52820976026</v>
+        <v>1.52302245204</v>
       </c>
       <c r="Q19">
-        <v>1.65820976026</v>
+        <v>1.65302245204</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.114965938301125</v>
+        <v>0.1156123826742548</v>
       </c>
       <c r="T19">
-        <v>1.348172875982186</v>
+        <v>1.360773280040765</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.32973788474825</v>
+        <v>17.31141911337334</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.101424249392889</v>
+        <v>0.1011725685958441</v>
       </c>
       <c r="C20">
-        <v>11.44002032948158</v>
+        <v>11.3123762881726</v>
       </c>
       <c r="D20">
-        <v>8.498020329481578</v>
+        <v>8.511376288172603</v>
       </c>
       <c r="E20">
-        <v>-3.712</v>
+        <v>-3.571</v>
       </c>
       <c r="F20">
-        <v>2.538</v>
+        <v>2.679</v>
       </c>
       <c r="G20">
         <v>5.48</v>
@@ -2921,28 +2921,28 @@
         <v>2.21</v>
       </c>
       <c r="M20">
-        <v>0.1276614</v>
+        <v>0.1347537</v>
       </c>
       <c r="N20">
-        <v>2.0823386</v>
+        <v>2.0752463</v>
       </c>
       <c r="O20">
-        <v>0.55931614796</v>
+        <v>0.55741115618</v>
       </c>
       <c r="P20">
-        <v>1.52302245204</v>
+        <v>1.51783514382</v>
       </c>
       <c r="Q20">
-        <v>1.65302245204</v>
+        <v>1.64783514382</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1156123826742548</v>
+        <v>0.1162747886368446</v>
       </c>
       <c r="T20">
-        <v>1.360773280040765</v>
+        <v>1.37368480518721</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.31141911337335</v>
+        <v>16.40029179161685</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1011725685958441</v>
+        <v>0.1009208877987993</v>
       </c>
       <c r="C21">
-        <v>11.3123762881726</v>
+        <v>11.18477429487513</v>
       </c>
       <c r="D21">
-        <v>8.511376288172603</v>
+        <v>8.524774294875135</v>
       </c>
       <c r="E21">
-        <v>-3.571</v>
+        <v>-3.43</v>
       </c>
       <c r="F21">
-        <v>2.679</v>
+        <v>2.82</v>
       </c>
       <c r="G21">
         <v>5.48</v>
@@ -3003,28 +3003,28 @@
         <v>2.21</v>
       </c>
       <c r="M21">
-        <v>0.1347537</v>
+        <v>0.141846</v>
       </c>
       <c r="N21">
-        <v>2.0752463</v>
+        <v>2.068154</v>
       </c>
       <c r="O21">
-        <v>0.55741115618</v>
+        <v>0.5555061644</v>
       </c>
       <c r="P21">
-        <v>1.51783514382</v>
+        <v>1.5126478356</v>
       </c>
       <c r="Q21">
-        <v>1.64783514382</v>
+        <v>1.6426478356</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1162747886368446</v>
+        <v>0.1169537547484991</v>
       </c>
       <c r="T21">
-        <v>1.37368480518721</v>
+        <v>1.386919118462316</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.40029179161685</v>
+        <v>15.58027720203601</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1009208877987993</v>
+        <v>0.1006692070017545</v>
       </c>
       <c r="C22">
-        <v>11.18477429487513</v>
+        <v>11.05721454846926</v>
       </c>
       <c r="D22">
-        <v>8.524774294875135</v>
+        <v>8.538214548469258</v>
       </c>
       <c r="E22">
-        <v>-3.43</v>
+        <v>-3.289</v>
       </c>
       <c r="F22">
-        <v>2.82</v>
+        <v>2.961</v>
       </c>
       <c r="G22">
         <v>5.48</v>
@@ -3085,28 +3085,28 @@
         <v>2.21</v>
       </c>
       <c r="M22">
-        <v>0.141846</v>
+        <v>0.1489383</v>
       </c>
       <c r="N22">
-        <v>2.068154</v>
+        <v>2.0610617</v>
       </c>
       <c r="O22">
-        <v>0.5555061644</v>
+        <v>0.55360117262</v>
       </c>
       <c r="P22">
-        <v>1.5126478356</v>
+        <v>1.50746052738</v>
       </c>
       <c r="Q22">
-        <v>1.6426478356</v>
+        <v>1.63746052738</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1169537547484991</v>
+        <v>0.1176499098756386</v>
       </c>
       <c r="T22">
-        <v>1.386919118462316</v>
+        <v>1.40048847764312</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.58027720203601</v>
+        <v>14.8383592400343</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1006692070017545</v>
+        <v>0.1004175262047097</v>
       </c>
       <c r="C23">
-        <v>11.05721454846926</v>
+        <v>10.92969724909126</v>
       </c>
       <c r="D23">
-        <v>8.538214548469258</v>
+        <v>8.55169724909126</v>
       </c>
       <c r="E23">
-        <v>-3.289</v>
+        <v>-3.148</v>
       </c>
       <c r="F23">
-        <v>2.961</v>
+        <v>3.102</v>
       </c>
       <c r="G23">
         <v>5.48</v>
@@ -3167,28 +3167,28 @@
         <v>2.21</v>
       </c>
       <c r="M23">
-        <v>0.1489383</v>
+        <v>0.1560306</v>
       </c>
       <c r="N23">
-        <v>2.0610617</v>
+        <v>2.0539694</v>
       </c>
       <c r="O23">
-        <v>0.55360117262</v>
+        <v>0.55169618084</v>
       </c>
       <c r="P23">
-        <v>1.50746052738</v>
+        <v>1.50227321916</v>
       </c>
       <c r="Q23">
-        <v>1.63746052738</v>
+        <v>1.63227321916</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1176499098756386</v>
+        <v>0.1183639151342432</v>
       </c>
       <c r="T23">
-        <v>1.40048847764312</v>
+        <v>1.414405769110612</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.8383592400343</v>
+        <v>14.16388836548728</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1004175262047097</v>
+        <v>0.1001658454076648</v>
       </c>
       <c r="C24">
-        <v>10.92969724909126</v>
+        <v>10.80222259814358</v>
       </c>
       <c r="D24">
-        <v>8.55169724909126</v>
+        <v>8.565222598143576</v>
       </c>
       <c r="E24">
-        <v>-3.148</v>
+        <v>-3.007</v>
       </c>
       <c r="F24">
-        <v>3.102</v>
+        <v>3.243</v>
       </c>
       <c r="G24">
         <v>5.48</v>
@@ -3249,28 +3249,28 @@
         <v>2.21</v>
       </c>
       <c r="M24">
-        <v>0.1560306</v>
+        <v>0.1631229</v>
       </c>
       <c r="N24">
-        <v>2.0539694</v>
+        <v>2.0468771</v>
       </c>
       <c r="O24">
-        <v>0.55169618084</v>
+        <v>0.54979118906</v>
       </c>
       <c r="P24">
-        <v>1.50227321916</v>
+        <v>1.49708591094</v>
       </c>
       <c r="Q24">
-        <v>1.63227321916</v>
+        <v>1.62708591094</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1183639151342432</v>
+        <v>0.1190964659839803</v>
       </c>
       <c r="T24">
-        <v>1.414405769110612</v>
+        <v>1.428684548668169</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.16388836548728</v>
+        <v>13.54806713220523</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1001658454076648</v>
+        <v>0.09991416461062</v>
       </c>
       <c r="C25">
-        <v>10.80222259814358</v>
+        <v>10.6747907983048</v>
       </c>
       <c r="D25">
-        <v>8.565222598143576</v>
+        <v>8.578790798304798</v>
       </c>
       <c r="E25">
-        <v>-3.007</v>
+        <v>-2.866</v>
       </c>
       <c r="F25">
-        <v>3.243</v>
+        <v>3.384</v>
       </c>
       <c r="G25">
         <v>5.48</v>
@@ -3331,28 +3331,28 @@
         <v>2.21</v>
       </c>
       <c r="M25">
-        <v>0.1631229</v>
+        <v>0.1702152</v>
       </c>
       <c r="N25">
-        <v>2.0468771</v>
+        <v>2.0397848</v>
       </c>
       <c r="O25">
-        <v>0.54979118906</v>
+        <v>0.54788619728</v>
       </c>
       <c r="P25">
-        <v>1.49708591094</v>
+        <v>1.49189860272</v>
       </c>
       <c r="Q25">
-        <v>1.62708591094</v>
+        <v>1.62189860272</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1190964659839803</v>
+        <v>0.1198482944876579</v>
       </c>
       <c r="T25">
-        <v>1.428684548668169</v>
+        <v>1.443339085582504</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.54806713220523</v>
+        <v>12.98356433503001</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09991416461062</v>
+        <v>0.09993675881357518</v>
       </c>
       <c r="C26">
-        <v>10.6747907983048</v>
+        <v>10.5325709808231</v>
       </c>
       <c r="D26">
-        <v>8.578790798304798</v>
+        <v>8.577570980823097</v>
       </c>
       <c r="E26">
-        <v>-2.866</v>
+        <v>-2.725</v>
       </c>
       <c r="F26">
-        <v>3.384</v>
+        <v>3.525</v>
       </c>
       <c r="G26">
         <v>5.48</v>
@@ -3413,45 +3413,45 @@
         <v>2.21</v>
       </c>
       <c r="M26">
-        <v>0.1702152</v>
+        <v>0.182595</v>
       </c>
       <c r="N26">
-        <v>2.0397848</v>
+        <v>2.027405</v>
       </c>
       <c r="O26">
-        <v>0.54788619728</v>
+        <v>0.544560983</v>
       </c>
       <c r="P26">
-        <v>1.49189860272</v>
+        <v>1.482844017</v>
       </c>
       <c r="Q26">
-        <v>1.62189860272</v>
+        <v>1.612844017</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1198482944876579</v>
+        <v>0.1206201717514336</v>
       </c>
       <c r="T26">
-        <v>1.443339085582503</v>
+        <v>1.458384410147887</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.2686</v>
       </c>
       <c r="W26">
-        <v>0.03678942</v>
+        <v>0.03788652</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.98356433503001</v>
+        <v>12.10328869903338</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09993675881357518</v>
+        <v>0.09969604901653037</v>
       </c>
       <c r="C27">
-        <v>10.5325709808231</v>
+        <v>10.40458430417477</v>
       </c>
       <c r="D27">
-        <v>8.577570980823097</v>
+        <v>8.59058430417477</v>
       </c>
       <c r="E27">
-        <v>-2.725</v>
+        <v>-2.584</v>
       </c>
       <c r="F27">
-        <v>3.525</v>
+        <v>3.666</v>
       </c>
       <c r="G27">
         <v>5.48</v>
@@ -3495,28 +3495,28 @@
         <v>2.21</v>
       </c>
       <c r="M27">
-        <v>0.182595</v>
+        <v>0.1898988</v>
       </c>
       <c r="N27">
-        <v>2.027405</v>
+        <v>2.0201012</v>
       </c>
       <c r="O27">
-        <v>0.544560983</v>
+        <v>0.54259918232</v>
       </c>
       <c r="P27">
-        <v>1.482844017</v>
+        <v>1.47750201768</v>
       </c>
       <c r="Q27">
-        <v>1.612844017</v>
+        <v>1.60750201768</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1206201717514336</v>
+        <v>0.1214129105628789</v>
       </c>
       <c r="T27">
-        <v>1.458384410147887</v>
+        <v>1.47383636510693</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.10328869903338</v>
+        <v>11.6377775952244</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09969604901653037</v>
+        <v>0.09945533921948553</v>
       </c>
       <c r="C28">
-        <v>10.40458430417477</v>
+        <v>10.27663717342979</v>
       </c>
       <c r="D28">
-        <v>8.59058430417477</v>
+        <v>8.603637173429791</v>
       </c>
       <c r="E28">
-        <v>-2.584</v>
+        <v>-2.443</v>
       </c>
       <c r="F28">
-        <v>3.666</v>
+        <v>3.807</v>
       </c>
       <c r="G28">
         <v>5.48</v>
@@ -3577,28 +3577,28 @@
         <v>2.21</v>
       </c>
       <c r="M28">
-        <v>0.1898988</v>
+        <v>0.1972026</v>
       </c>
       <c r="N28">
-        <v>2.0201012</v>
+        <v>2.0127974</v>
       </c>
       <c r="O28">
-        <v>0.54259918232</v>
+        <v>0.5406373816400001</v>
       </c>
       <c r="P28">
-        <v>1.47750201768</v>
+        <v>1.47216001836</v>
       </c>
       <c r="Q28">
-        <v>1.60750201768</v>
+        <v>1.60216001836</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1214129105628789</v>
+        <v>0.1222273682458706</v>
       </c>
       <c r="T28">
-        <v>1.47383636510693</v>
+        <v>1.489711661297727</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.6377775952244</v>
+        <v>11.20674879540128</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09945533921948553</v>
+        <v>0.09921462942244071</v>
       </c>
       <c r="C29">
-        <v>10.27663717342979</v>
+        <v>10.14872976912524</v>
       </c>
       <c r="D29">
-        <v>8.603637173429791</v>
+        <v>8.616729769125239</v>
       </c>
       <c r="E29">
-        <v>-2.443</v>
+        <v>-2.302</v>
       </c>
       <c r="F29">
-        <v>3.807</v>
+        <v>3.948</v>
       </c>
       <c r="G29">
         <v>5.48</v>
@@ -3659,28 +3659,28 @@
         <v>2.21</v>
       </c>
       <c r="M29">
-        <v>0.1972026</v>
+        <v>0.2045064</v>
       </c>
       <c r="N29">
-        <v>2.0127974</v>
+        <v>2.0054936</v>
       </c>
       <c r="O29">
-        <v>0.5406373816400001</v>
+        <v>0.53867558096</v>
       </c>
       <c r="P29">
-        <v>1.47216001836</v>
+        <v>1.46681801904</v>
       </c>
       <c r="Q29">
-        <v>1.60216001836</v>
+        <v>1.59681801904</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1222273682458706</v>
+        <v>0.1230644497533899</v>
       </c>
       <c r="T29">
-        <v>1.489711661297727</v>
+        <v>1.506027937938268</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.20674879540128</v>
+        <v>10.80650776699409</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09921462942244071</v>
+        <v>0.09897391962539588</v>
       </c>
       <c r="C30">
-        <v>10.14872976912524</v>
+        <v>10.02086227289881</v>
       </c>
       <c r="D30">
-        <v>8.616729769125239</v>
+        <v>8.629862272898807</v>
       </c>
       <c r="E30">
-        <v>-2.302</v>
+        <v>-2.161</v>
       </c>
       <c r="F30">
-        <v>3.948</v>
+        <v>4.089</v>
       </c>
       <c r="G30">
         <v>5.48</v>
@@ -3741,28 +3741,28 @@
         <v>2.21</v>
       </c>
       <c r="M30">
-        <v>0.2045064</v>
+        <v>0.2118102</v>
       </c>
       <c r="N30">
-        <v>2.0054936</v>
+        <v>1.9981898</v>
       </c>
       <c r="O30">
-        <v>0.53867558096</v>
+        <v>0.5367137802800001</v>
       </c>
       <c r="P30">
-        <v>1.46681801904</v>
+        <v>1.46147601972</v>
       </c>
       <c r="Q30">
-        <v>1.59681801904</v>
+        <v>1.59147601972</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1230644497533899</v>
+        <v>0.1239251110216844</v>
       </c>
       <c r="T30">
-        <v>1.506027937938268</v>
+        <v>1.522803828005304</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.80650776699409</v>
+        <v>10.43386956813222</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09897391962539588</v>
+        <v>0.09873320982835106</v>
       </c>
       <c r="C31">
-        <v>10.02086227289881</v>
+        <v>9.893034867497185</v>
       </c>
       <c r="D31">
-        <v>8.629862272898807</v>
+        <v>8.643034867497185</v>
       </c>
       <c r="E31">
-        <v>-2.161</v>
+        <v>-2.02</v>
       </c>
       <c r="F31">
-        <v>4.089</v>
+        <v>4.23</v>
       </c>
       <c r="G31">
         <v>5.48</v>
@@ -3823,28 +3823,28 @@
         <v>2.21</v>
       </c>
       <c r="M31">
-        <v>0.2118102</v>
+        <v>0.219114</v>
       </c>
       <c r="N31">
-        <v>1.9981898</v>
+        <v>1.990886</v>
       </c>
       <c r="O31">
-        <v>0.5367137802800001</v>
+        <v>0.5347519796</v>
       </c>
       <c r="P31">
-        <v>1.46147601972</v>
+        <v>1.4561340204</v>
       </c>
       <c r="Q31">
-        <v>1.59147601972</v>
+        <v>1.5861340204</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1239251110216844</v>
+        <v>0.1248103626119301</v>
       </c>
       <c r="T31">
-        <v>1.522803828005304</v>
+        <v>1.540059029217111</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.43386956813223</v>
+        <v>10.08607391586115</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09873320982835106</v>
+        <v>0.09887794783130624</v>
       </c>
       <c r="C32">
-        <v>9.893034867497185</v>
+        <v>9.744109414118004</v>
       </c>
       <c r="D32">
-        <v>8.643034867497185</v>
+        <v>8.635109414118002</v>
       </c>
       <c r="E32">
-        <v>-2.02</v>
+        <v>-1.879</v>
       </c>
       <c r="F32">
-        <v>4.23</v>
+        <v>4.371</v>
       </c>
       <c r="G32">
         <v>5.48</v>
@@ -3905,45 +3905,45 @@
         <v>2.21</v>
       </c>
       <c r="M32">
-        <v>0.219114</v>
+        <v>0.2338485</v>
       </c>
       <c r="N32">
-        <v>1.990886</v>
+        <v>1.9761515</v>
       </c>
       <c r="O32">
-        <v>0.5347519796</v>
+        <v>0.5307942929</v>
       </c>
       <c r="P32">
-        <v>1.4561340204</v>
+        <v>1.4453572071</v>
       </c>
       <c r="Q32">
-        <v>1.5861340204</v>
+        <v>1.5753572071</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1248103626119301</v>
+        <v>0.1257212736685598</v>
       </c>
       <c r="T32">
-        <v>1.540059029217111</v>
+        <v>1.557814381188682</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.2686</v>
       </c>
       <c r="W32">
-        <v>0.03788652</v>
+        <v>0.0391299</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.08607391586115</v>
+        <v>9.450563078232276</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09887794783130624</v>
+        <v>0.09864967183426142</v>
       </c>
       <c r="C33">
-        <v>9.744109414118004</v>
+        <v>9.615615802438882</v>
       </c>
       <c r="D33">
-        <v>8.635109414118002</v>
+        <v>8.647615802438882</v>
       </c>
       <c r="E33">
-        <v>-1.879</v>
+        <v>-1.738</v>
       </c>
       <c r="F33">
-        <v>4.371</v>
+        <v>4.512</v>
       </c>
       <c r="G33">
         <v>5.48</v>
@@ -3987,28 +3987,28 @@
         <v>2.21</v>
       </c>
       <c r="M33">
-        <v>0.2338485</v>
+        <v>0.241392</v>
       </c>
       <c r="N33">
-        <v>1.9761515</v>
+        <v>1.968608</v>
       </c>
       <c r="O33">
-        <v>0.5307942929</v>
+        <v>0.5287681088</v>
       </c>
       <c r="P33">
-        <v>1.4453572071</v>
+        <v>1.4398398912</v>
       </c>
       <c r="Q33">
-        <v>1.5753572071</v>
+        <v>1.5698398912</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1257212736685598</v>
+        <v>0.126658976226855</v>
       </c>
       <c r="T33">
-        <v>1.557814381188682</v>
+        <v>1.576091949394711</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.450563078232276</v>
+        <v>9.155232982037516</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09864967183426142</v>
+        <v>0.0984213958372166</v>
       </c>
       <c r="C34">
-        <v>9.615615802438882</v>
+        <v>9.48715846976933</v>
       </c>
       <c r="D34">
-        <v>8.647615802438882</v>
+        <v>8.66015846976933</v>
       </c>
       <c r="E34">
-        <v>-1.738</v>
+        <v>-1.597</v>
       </c>
       <c r="F34">
-        <v>4.512</v>
+        <v>4.653</v>
       </c>
       <c r="G34">
         <v>5.48</v>
@@ -4069,28 +4069,28 @@
         <v>2.21</v>
       </c>
       <c r="M34">
-        <v>0.241392</v>
+        <v>0.2489355</v>
       </c>
       <c r="N34">
-        <v>1.968608</v>
+        <v>1.9610645</v>
       </c>
       <c r="O34">
-        <v>0.5287681088</v>
+        <v>0.5267419247</v>
       </c>
       <c r="P34">
-        <v>1.4398398912</v>
+        <v>1.4343225753</v>
       </c>
       <c r="Q34">
-        <v>1.5698398912</v>
+        <v>1.5643225753</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.126658976226855</v>
+        <v>0.1276246699062934</v>
       </c>
       <c r="T34">
-        <v>1.576091949394711</v>
+        <v>1.594915116651665</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.155232982037516</v>
+        <v>8.87780167955153</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0984213958372166</v>
+        <v>0.09819311984017179</v>
       </c>
       <c r="C35">
-        <v>9.48715846976933</v>
+        <v>9.358737574197946</v>
       </c>
       <c r="D35">
-        <v>8.66015846976933</v>
+        <v>8.672737574197946</v>
       </c>
       <c r="E35">
-        <v>-1.597</v>
+        <v>-1.456</v>
       </c>
       <c r="F35">
-        <v>4.653</v>
+        <v>4.794</v>
       </c>
       <c r="G35">
         <v>5.48</v>
@@ -4151,28 +4151,28 @@
         <v>2.21</v>
       </c>
       <c r="M35">
-        <v>0.2489355</v>
+        <v>0.256479</v>
       </c>
       <c r="N35">
-        <v>1.9610645</v>
+        <v>1.953521</v>
       </c>
       <c r="O35">
-        <v>0.5267419247</v>
+        <v>0.5247157405999999</v>
       </c>
       <c r="P35">
-        <v>1.4343225753</v>
+        <v>1.4288052594</v>
       </c>
       <c r="Q35">
-        <v>1.5643225753</v>
+        <v>1.5588052594</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1276246699062934</v>
+        <v>0.1286196270305633</v>
       </c>
       <c r="T35">
-        <v>1.594915116651665</v>
+        <v>1.614308682916407</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.87780167955153</v>
+        <v>8.616689865447071</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09819311984017179</v>
+        <v>0.09796484384312695</v>
       </c>
       <c r="C36">
-        <v>9.358737574197946</v>
+        <v>9.230353274733183</v>
       </c>
       <c r="D36">
-        <v>8.672737574197946</v>
+        <v>8.685353274733183</v>
       </c>
       <c r="E36">
-        <v>-1.456</v>
+        <v>-1.315</v>
       </c>
       <c r="F36">
-        <v>4.794</v>
+        <v>4.935</v>
       </c>
       <c r="G36">
         <v>5.48</v>
@@ -4233,28 +4233,28 @@
         <v>2.21</v>
       </c>
       <c r="M36">
-        <v>0.256479</v>
+        <v>0.2640225</v>
       </c>
       <c r="N36">
-        <v>1.953521</v>
+        <v>1.9459775</v>
       </c>
       <c r="O36">
-        <v>0.5247157405999999</v>
+        <v>0.5226895565</v>
       </c>
       <c r="P36">
-        <v>1.4288052594</v>
+        <v>1.4232879435</v>
       </c>
       <c r="Q36">
-        <v>1.5588052594</v>
+        <v>1.5532879435</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1286196270305633</v>
+        <v>0.1296451982201953</v>
       </c>
       <c r="T36">
-        <v>1.614308682916407</v>
+        <v>1.634298974296986</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.616689865447071</v>
+        <v>8.370498726434299</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09796484384312695</v>
+        <v>0.09773656784608213</v>
       </c>
       <c r="C37">
-        <v>9.230353274733183</v>
+        <v>9.102005731310035</v>
       </c>
       <c r="D37">
-        <v>8.685353274733183</v>
+        <v>8.698005731310035</v>
       </c>
       <c r="E37">
-        <v>-1.315</v>
+        <v>-1.173999999999999</v>
       </c>
       <c r="F37">
-        <v>4.935</v>
+        <v>5.076000000000001</v>
       </c>
       <c r="G37">
         <v>5.48</v>
@@ -4315,28 +4315,28 @@
         <v>2.21</v>
       </c>
       <c r="M37">
-        <v>0.2640225</v>
+        <v>0.271566</v>
       </c>
       <c r="N37">
-        <v>1.9459775</v>
+        <v>1.938434</v>
       </c>
       <c r="O37">
-        <v>0.5226895565</v>
+        <v>0.5206633724</v>
       </c>
       <c r="P37">
-        <v>1.4232879435</v>
+        <v>1.4177706276</v>
       </c>
       <c r="Q37">
-        <v>1.5532879435</v>
+        <v>1.5477706276</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1296451982201953</v>
+        <v>0.1307028185095034</v>
       </c>
       <c r="T37">
-        <v>1.634298974296986</v>
+        <v>1.654913962283209</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.370498726434299</v>
+        <v>8.137984872922235</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09773656784608213</v>
+        <v>0.0975082918490373</v>
       </c>
       <c r="C38">
-        <v>9.102005731310037</v>
+        <v>8.973695104796807</v>
       </c>
       <c r="D38">
-        <v>8.698005731310035</v>
+        <v>8.710695104796805</v>
       </c>
       <c r="E38">
-        <v>-1.174</v>
+        <v>-1.033</v>
       </c>
       <c r="F38">
-        <v>5.076</v>
+        <v>5.217</v>
       </c>
       <c r="G38">
         <v>5.48</v>
@@ -4397,28 +4397,28 @@
         <v>2.21</v>
       </c>
       <c r="M38">
-        <v>0.271566</v>
+        <v>0.2791095</v>
       </c>
       <c r="N38">
-        <v>1.938434</v>
+        <v>1.9308905</v>
       </c>
       <c r="O38">
-        <v>0.5206633724</v>
+        <v>0.5186371883000001</v>
       </c>
       <c r="P38">
-        <v>1.4177706276</v>
+        <v>1.4122533117</v>
       </c>
       <c r="Q38">
-        <v>1.5477706276</v>
+        <v>1.5422533117</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1307028185095033</v>
+        <v>0.131794014046091</v>
       </c>
       <c r="T38">
-        <v>1.654913962283208</v>
+        <v>1.676183394332486</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.137984872922237</v>
+        <v>7.918039335816231</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0975082918490373</v>
+        <v>0.09728001585199249</v>
       </c>
       <c r="C39">
-        <v>8.973695104796807</v>
+        <v>8.845421557001924</v>
       </c>
       <c r="D39">
-        <v>8.710695104796805</v>
+        <v>8.723421557001924</v>
       </c>
       <c r="E39">
-        <v>-1.033</v>
+        <v>-0.8920000000000003</v>
       </c>
       <c r="F39">
-        <v>5.217</v>
+        <v>5.358</v>
       </c>
       <c r="G39">
         <v>5.48</v>
@@ -4479,28 +4479,28 @@
         <v>2.21</v>
       </c>
       <c r="M39">
-        <v>0.2791095</v>
+        <v>0.286653</v>
       </c>
       <c r="N39">
-        <v>1.9308905</v>
+        <v>1.923347</v>
       </c>
       <c r="O39">
-        <v>0.5186371883000001</v>
+        <v>0.5166110041999999</v>
       </c>
       <c r="P39">
-        <v>1.4122533117</v>
+        <v>1.4067359958</v>
       </c>
       <c r="Q39">
-        <v>1.5422533117</v>
+        <v>1.5367359958</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.131794014046091</v>
+        <v>0.1329204094386976</v>
       </c>
       <c r="T39">
-        <v>1.676183394332486</v>
+        <v>1.69813893709303</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.918039335816231</v>
+        <v>7.70966987961054</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09728001585199249</v>
+        <v>0.09727993665494768</v>
       </c>
       <c r="C40">
-        <v>8.845421557001924</v>
+        <v>8.704425978712848</v>
       </c>
       <c r="D40">
-        <v>8.723421557001924</v>
+        <v>8.723425978712847</v>
       </c>
       <c r="E40">
-        <v>-0.8920000000000003</v>
+        <v>-0.7510000000000003</v>
       </c>
       <c r="F40">
-        <v>5.358</v>
+        <v>5.499</v>
       </c>
       <c r="G40">
         <v>5.48</v>
@@ -4561,45 +4561,45 @@
         <v>2.21</v>
       </c>
       <c r="M40">
-        <v>0.286653</v>
+        <v>0.2985957</v>
       </c>
       <c r="N40">
-        <v>1.923347</v>
+        <v>1.9114043</v>
       </c>
       <c r="O40">
-        <v>0.5166110041999999</v>
+        <v>0.51340319498</v>
       </c>
       <c r="P40">
-        <v>1.4067359958</v>
+        <v>1.39800110502</v>
       </c>
       <c r="Q40">
-        <v>1.5367359958</v>
+        <v>1.52800110502</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1329204094386976</v>
+        <v>0.1340837358277831</v>
       </c>
       <c r="T40">
-        <v>1.69813893709303</v>
+        <v>1.720814333714576</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.2686</v>
       </c>
       <c r="W40">
-        <v>0.0391299</v>
+        <v>0.03971502</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.70966987961054</v>
+        <v>7.401312209117547</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09727993665494768</v>
+        <v>0.09705751185790285</v>
       </c>
       <c r="C41">
-        <v>8.704425978712848</v>
+        <v>8.575862057955396</v>
       </c>
       <c r="D41">
-        <v>8.723425978712847</v>
+        <v>8.735862057955396</v>
       </c>
       <c r="E41">
-        <v>-0.7510000000000003</v>
+        <v>-0.6099999999999994</v>
       </c>
       <c r="F41">
-        <v>5.499</v>
+        <v>5.640000000000001</v>
       </c>
       <c r="G41">
         <v>5.48</v>
@@ -4643,28 +4643,28 @@
         <v>2.21</v>
       </c>
       <c r="M41">
-        <v>0.2985957</v>
+        <v>0.306252</v>
       </c>
       <c r="N41">
-        <v>1.9114043</v>
+        <v>1.903748</v>
       </c>
       <c r="O41">
-        <v>0.51340319498</v>
+        <v>0.5113467128</v>
       </c>
       <c r="P41">
-        <v>1.39800110502</v>
+        <v>1.3924012872</v>
       </c>
       <c r="Q41">
-        <v>1.52800110502</v>
+        <v>1.5224012872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1340837358277831</v>
+        <v>0.1352858397631714</v>
       </c>
       <c r="T41">
-        <v>1.720814333714576</v>
+        <v>1.744245576890173</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.401312209117547</v>
+        <v>7.216279403889606</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09705751185790285</v>
+        <v>0.09683508706085803</v>
       </c>
       <c r="C42">
-        <v>8.575862057955396</v>
+        <v>8.447333645462493</v>
       </c>
       <c r="D42">
-        <v>8.735862057955396</v>
+        <v>8.748333645462493</v>
       </c>
       <c r="E42">
-        <v>-0.6099999999999994</v>
+        <v>-0.4689999999999994</v>
       </c>
       <c r="F42">
-        <v>5.640000000000001</v>
+        <v>5.781000000000001</v>
       </c>
       <c r="G42">
         <v>5.48</v>
@@ -4725,28 +4725,28 @@
         <v>2.21</v>
       </c>
       <c r="M42">
-        <v>0.306252</v>
+        <v>0.3139083</v>
       </c>
       <c r="N42">
-        <v>1.903748</v>
+        <v>1.8960917</v>
       </c>
       <c r="O42">
-        <v>0.5113467128</v>
+        <v>0.50929023062</v>
       </c>
       <c r="P42">
-        <v>1.3924012872</v>
+        <v>1.38680146938</v>
       </c>
       <c r="Q42">
-        <v>1.5224012872</v>
+        <v>1.51680146938</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1352858397631714</v>
+        <v>0.1365286929845051</v>
       </c>
       <c r="T42">
-        <v>1.744245576890173</v>
+        <v>1.768471099495451</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.216279403889606</v>
+        <v>7.040272589160591</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09683508706085803</v>
+        <v>0.09661266226381318</v>
       </c>
       <c r="C43">
-        <v>8.447333645462493</v>
+        <v>8.318840893529666</v>
       </c>
       <c r="D43">
-        <v>8.748333645462493</v>
+        <v>8.760840893529666</v>
       </c>
       <c r="E43">
-        <v>-0.4689999999999994</v>
+        <v>-0.3279999999999994</v>
       </c>
       <c r="F43">
-        <v>5.781000000000001</v>
+        <v>5.922000000000001</v>
       </c>
       <c r="G43">
         <v>5.48</v>
@@ -4807,28 +4807,28 @@
         <v>2.21</v>
       </c>
       <c r="M43">
-        <v>0.3139083</v>
+        <v>0.3215646</v>
       </c>
       <c r="N43">
-        <v>1.8960917</v>
+        <v>1.8884354</v>
       </c>
       <c r="O43">
-        <v>0.50929023062</v>
+        <v>0.50723374844</v>
       </c>
       <c r="P43">
-        <v>1.38680146938</v>
+        <v>1.38120165156</v>
       </c>
       <c r="Q43">
-        <v>1.51680146938</v>
+        <v>1.51120165156</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1365286929845051</v>
+        <v>0.137814403213471</v>
       </c>
       <c r="T43">
-        <v>1.768471099495451</v>
+        <v>1.793531984949188</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.040272589160591</v>
+        <v>6.872647051323434</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0966126622638132</v>
+        <v>0.09639023746676839</v>
       </c>
       <c r="C44">
-        <v>8.318840893529664</v>
+        <v>8.190383955324602</v>
       </c>
       <c r="D44">
-        <v>8.760840893529664</v>
+        <v>8.773383955324601</v>
       </c>
       <c r="E44">
-        <v>-0.3280000000000003</v>
+        <v>-0.1870000000000003</v>
       </c>
       <c r="F44">
-        <v>5.922</v>
+        <v>6.063</v>
       </c>
       <c r="G44">
         <v>5.48</v>
@@ -4889,28 +4889,28 @@
         <v>2.21</v>
       </c>
       <c r="M44">
-        <v>0.3215646</v>
+        <v>0.3292209</v>
       </c>
       <c r="N44">
-        <v>1.8884354</v>
+        <v>1.8807791</v>
       </c>
       <c r="O44">
-        <v>0.50723374844</v>
+        <v>0.50517726626</v>
       </c>
       <c r="P44">
-        <v>1.38120165156</v>
+        <v>1.37560183374</v>
       </c>
       <c r="Q44">
-        <v>1.51120165156</v>
+        <v>1.50560183374</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.137814403213471</v>
+        <v>0.1391452260820498</v>
       </c>
       <c r="T44">
-        <v>1.793531984949188</v>
+        <v>1.81947219971709</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.872647051323436</v>
+        <v>6.712818050129868</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09639023746676839</v>
+        <v>0.09616781266972356</v>
       </c>
       <c r="C45">
-        <v>8.190383955324602</v>
+        <v>8.061962984893437</v>
       </c>
       <c r="D45">
-        <v>8.773383955324601</v>
+        <v>8.785962984893438</v>
       </c>
       <c r="E45">
-        <v>-0.1870000000000003</v>
+        <v>-0.04600000000000026</v>
       </c>
       <c r="F45">
-        <v>6.063</v>
+        <v>6.204</v>
       </c>
       <c r="G45">
         <v>5.48</v>
@@ -4971,28 +4971,28 @@
         <v>2.21</v>
       </c>
       <c r="M45">
-        <v>0.3292209</v>
+        <v>0.3368772</v>
       </c>
       <c r="N45">
-        <v>1.8807791</v>
+        <v>1.8731228</v>
       </c>
       <c r="O45">
-        <v>0.50517726626</v>
+        <v>0.50312078408</v>
       </c>
       <c r="P45">
-        <v>1.37560183374</v>
+        <v>1.37000201592</v>
       </c>
       <c r="Q45">
-        <v>1.50560183374</v>
+        <v>1.50000201592</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1391452260820498</v>
+        <v>0.1405235783387921</v>
       </c>
       <c r="T45">
-        <v>1.81947219971709</v>
+        <v>1.846338850726703</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.712818050129868</v>
+        <v>6.560254003536007</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09616781266972356</v>
+        <v>0.09594538787267873</v>
       </c>
       <c r="C46">
-        <v>8.061962984893437</v>
+        <v>7.933578137167031</v>
       </c>
       <c r="D46">
-        <v>8.785962984893438</v>
+        <v>8.798578137167031</v>
       </c>
       <c r="E46">
-        <v>-0.04600000000000026</v>
+        <v>0.09499999999999975</v>
       </c>
       <c r="F46">
-        <v>6.204</v>
+        <v>6.345</v>
       </c>
       <c r="G46">
         <v>5.48</v>
@@ -5053,28 +5053,28 @@
         <v>2.21</v>
       </c>
       <c r="M46">
-        <v>0.3368772</v>
+        <v>0.3445335</v>
       </c>
       <c r="N46">
-        <v>1.8731228</v>
+        <v>1.8654665</v>
       </c>
       <c r="O46">
-        <v>0.50312078408</v>
+        <v>0.5010643019</v>
       </c>
       <c r="P46">
-        <v>1.37000201592</v>
+        <v>1.3644021981</v>
       </c>
       <c r="Q46">
-        <v>1.50000201592</v>
+        <v>1.4944021981</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1405235783387921</v>
+        <v>0.1419520524957795</v>
       </c>
       <c r="T46">
-        <v>1.846338850726703</v>
+        <v>1.874182470863939</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.560254003536007</v>
+        <v>6.414470581235206</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09594538787267873</v>
+        <v>0.09572296307563391</v>
       </c>
       <c r="C47">
-        <v>7.933578137167031</v>
+        <v>7.805229567967344</v>
       </c>
       <c r="D47">
-        <v>8.798578137167031</v>
+        <v>8.811229567967343</v>
       </c>
       <c r="E47">
-        <v>0.09499999999999975</v>
+        <v>0.2359999999999998</v>
       </c>
       <c r="F47">
-        <v>6.345</v>
+        <v>6.486</v>
       </c>
       <c r="G47">
         <v>5.48</v>
@@ -5135,28 +5135,28 @@
         <v>2.21</v>
       </c>
       <c r="M47">
-        <v>0.3445335</v>
+        <v>0.3521898</v>
       </c>
       <c r="N47">
-        <v>1.8654665</v>
+        <v>1.8578102</v>
       </c>
       <c r="O47">
-        <v>0.5010643019</v>
+        <v>0.49900781972</v>
       </c>
       <c r="P47">
-        <v>1.3644021981</v>
+        <v>1.35880238028</v>
       </c>
       <c r="Q47">
-        <v>1.4944021981</v>
+        <v>1.48880238028</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1419520524957795</v>
+        <v>0.1434334331030258</v>
       </c>
       <c r="T47">
-        <v>1.874182470863939</v>
+        <v>1.903057336191442</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.414470581235206</v>
+        <v>6.275025568599658</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09572296307563391</v>
+        <v>0.09550053827858909</v>
       </c>
       <c r="C48">
-        <v>7.805229567967344</v>
+        <v>7.676917434013848</v>
       </c>
       <c r="D48">
-        <v>8.811229567967343</v>
+        <v>8.823917434013849</v>
       </c>
       <c r="E48">
-        <v>0.2359999999999998</v>
+        <v>0.3770000000000007</v>
       </c>
       <c r="F48">
-        <v>6.486</v>
+        <v>6.627000000000001</v>
       </c>
       <c r="G48">
         <v>5.48</v>
@@ -5217,28 +5217,28 @@
         <v>2.21</v>
       </c>
       <c r="M48">
-        <v>0.3521898</v>
+        <v>0.3598461000000001</v>
       </c>
       <c r="N48">
-        <v>1.8578102</v>
+        <v>1.8501539</v>
       </c>
       <c r="O48">
-        <v>0.49900781972</v>
+        <v>0.49695133754</v>
       </c>
       <c r="P48">
-        <v>1.35880238028</v>
+        <v>1.35320256246</v>
       </c>
       <c r="Q48">
-        <v>1.48880238028</v>
+        <v>1.48320256246</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1434334331030258</v>
+        <v>0.1449707148652624</v>
       </c>
       <c r="T48">
-        <v>1.903057336191442</v>
+        <v>1.933021819078475</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.275025568599658</v>
+        <v>6.141514386289026</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09550053827858909</v>
+        <v>0.09562918548154425</v>
       </c>
       <c r="C49">
-        <v>7.676917434013848</v>
+        <v>7.528574508957169</v>
       </c>
       <c r="D49">
-        <v>8.823917434013849</v>
+        <v>8.816574508957169</v>
       </c>
       <c r="E49">
-        <v>0.3770000000000007</v>
+        <v>0.5180000000000007</v>
       </c>
       <c r="F49">
-        <v>6.627000000000001</v>
+        <v>6.768000000000001</v>
       </c>
       <c r="G49">
         <v>5.48</v>
@@ -5299,45 +5299,45 @@
         <v>2.21</v>
       </c>
       <c r="M49">
-        <v>0.3598461000000001</v>
+        <v>0.3742704000000001</v>
       </c>
       <c r="N49">
-        <v>1.8501539</v>
+        <v>1.8357296</v>
       </c>
       <c r="O49">
-        <v>0.49695133754</v>
+        <v>0.49307697056</v>
       </c>
       <c r="P49">
-        <v>1.35320256246</v>
+        <v>1.34265262944</v>
       </c>
       <c r="Q49">
-        <v>1.48320256246</v>
+        <v>1.47265262944</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1449707148652624</v>
+        <v>0.1465671228491236</v>
       </c>
       <c r="T49">
-        <v>1.933021819078475</v>
+        <v>1.964138782076546</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.2686</v>
       </c>
       <c r="W49">
-        <v>0.03971502</v>
+        <v>0.04044642</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.141514386289026</v>
+        <v>5.904821754538963</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09562918548154425</v>
+        <v>0.09541407468449944</v>
       </c>
       <c r="C50">
-        <v>7.52857450895717</v>
+        <v>7.39985947968139</v>
       </c>
       <c r="D50">
-        <v>8.816574508957169</v>
+        <v>8.828859479681389</v>
       </c>
       <c r="E50">
-        <v>0.5179999999999998</v>
+        <v>0.6589999999999998</v>
       </c>
       <c r="F50">
-        <v>6.768</v>
+        <v>6.909</v>
       </c>
       <c r="G50">
         <v>5.48</v>
@@ -5381,28 +5381,28 @@
         <v>2.21</v>
       </c>
       <c r="M50">
-        <v>0.3742704</v>
+        <v>0.3820677</v>
       </c>
       <c r="N50">
-        <v>1.8357296</v>
+        <v>1.8279323</v>
       </c>
       <c r="O50">
-        <v>0.49307697056</v>
+        <v>0.49098261578</v>
       </c>
       <c r="P50">
-        <v>1.34265262944</v>
+        <v>1.33694968422</v>
       </c>
       <c r="Q50">
-        <v>1.47265262944</v>
+        <v>1.46694968422</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1465671228491236</v>
+        <v>0.148226135067646</v>
       </c>
       <c r="T50">
-        <v>1.964138782076546</v>
+        <v>1.996476018133366</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.904821754538965</v>
+        <v>5.784315188119802</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09541407468449944</v>
+        <v>0.09519896388745462</v>
       </c>
       <c r="C51">
-        <v>7.39985947968139</v>
+        <v>7.27117873380918</v>
       </c>
       <c r="D51">
-        <v>8.828859479681389</v>
+        <v>8.84117873380918</v>
       </c>
       <c r="E51">
-        <v>0.6589999999999998</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="F51">
-        <v>6.909</v>
+        <v>7.05</v>
       </c>
       <c r="G51">
         <v>5.48</v>
@@ -5463,28 +5463,28 @@
         <v>2.21</v>
       </c>
       <c r="M51">
-        <v>0.3820677</v>
+        <v>0.389865</v>
       </c>
       <c r="N51">
-        <v>1.8279323</v>
+        <v>1.820135</v>
       </c>
       <c r="O51">
-        <v>0.49098261578</v>
+        <v>0.488888261</v>
       </c>
       <c r="P51">
-        <v>1.33694968422</v>
+        <v>1.331246739</v>
       </c>
       <c r="Q51">
-        <v>1.46694968422</v>
+        <v>1.461246739</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.148226135067646</v>
+        <v>0.1499515077749092</v>
       </c>
       <c r="T51">
-        <v>1.996476018133366</v>
+        <v>2.030106743632458</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.784315188119802</v>
+        <v>5.668628884357406</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09519896388745462</v>
+        <v>0.09498385309040978</v>
       </c>
       <c r="C52">
-        <v>7.27117873380918</v>
+        <v>7.142532415052007</v>
       </c>
       <c r="D52">
-        <v>8.84117873380918</v>
+        <v>8.853532415052006</v>
       </c>
       <c r="E52">
-        <v>0.7999999999999998</v>
+        <v>0.9409999999999998</v>
       </c>
       <c r="F52">
-        <v>7.05</v>
+        <v>7.191</v>
       </c>
       <c r="G52">
         <v>5.48</v>
@@ -5545,28 +5545,28 @@
         <v>2.21</v>
       </c>
       <c r="M52">
-        <v>0.389865</v>
+        <v>0.3976623</v>
       </c>
       <c r="N52">
-        <v>1.820135</v>
+        <v>1.8123377</v>
       </c>
       <c r="O52">
-        <v>0.488888261</v>
+        <v>0.48679390622</v>
       </c>
       <c r="P52">
-        <v>1.331246739</v>
+        <v>1.32554379378</v>
       </c>
       <c r="Q52">
-        <v>1.461246739</v>
+        <v>1.45554379378</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1499515077749092</v>
+        <v>0.1517473038579792</v>
       </c>
       <c r="T52">
-        <v>2.030106743632458</v>
+        <v>2.065110151804983</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.668628884357406</v>
+        <v>5.557479298389613</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09498385309040978</v>
+        <v>0.09476874229336499</v>
       </c>
       <c r="C53">
-        <v>7.142532415052007</v>
+        <v>7.013920667925674</v>
       </c>
       <c r="D53">
-        <v>8.853532415052006</v>
+        <v>8.865920667925673</v>
       </c>
       <c r="E53">
-        <v>0.9409999999999998</v>
+        <v>1.082</v>
       </c>
       <c r="F53">
-        <v>7.191</v>
+        <v>7.332</v>
       </c>
       <c r="G53">
         <v>5.48</v>
@@ -5627,28 +5627,28 @@
         <v>2.21</v>
       </c>
       <c r="M53">
-        <v>0.3976623</v>
+        <v>0.4054596</v>
       </c>
       <c r="N53">
-        <v>1.8123377</v>
+        <v>1.8045404</v>
       </c>
       <c r="O53">
-        <v>0.48679390622</v>
+        <v>0.48469955144</v>
       </c>
       <c r="P53">
-        <v>1.32554379378</v>
+        <v>1.31984084856</v>
       </c>
       <c r="Q53">
-        <v>1.45554379378</v>
+        <v>1.44984084856</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1517473038579792</v>
+        <v>0.1536179247778437</v>
       </c>
       <c r="T53">
-        <v>2.065110151804983</v>
+        <v>2.10157203531803</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.557479298389613</v>
+        <v>5.450604696497505</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09476874229336499</v>
+        <v>0.09455363149632015</v>
       </c>
       <c r="C54">
-        <v>7.013920667925674</v>
+        <v>6.885343637755983</v>
       </c>
       <c r="D54">
-        <v>8.865920667925673</v>
+        <v>8.878343637755982</v>
       </c>
       <c r="E54">
-        <v>1.082</v>
+        <v>1.223</v>
       </c>
       <c r="F54">
-        <v>7.332</v>
+        <v>7.473</v>
       </c>
       <c r="G54">
         <v>5.48</v>
@@ -5709,28 +5709,28 @@
         <v>2.21</v>
       </c>
       <c r="M54">
-        <v>0.4054596</v>
+        <v>0.4132569</v>
       </c>
       <c r="N54">
-        <v>1.8045404</v>
+        <v>1.7967431</v>
       </c>
       <c r="O54">
-        <v>0.48469955144</v>
+        <v>0.48260519666</v>
       </c>
       <c r="P54">
-        <v>1.31984084856</v>
+        <v>1.31413790334</v>
       </c>
       <c r="Q54">
-        <v>1.44984084856</v>
+        <v>1.44413790334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1536179247778437</v>
+        <v>0.1555681465879152</v>
       </c>
       <c r="T54">
-        <v>2.10157203531803</v>
+        <v>2.13958548834227</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.450604696497505</v>
+        <v>5.347763098450383</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09455363149632015</v>
+        <v>0.09433852069927533</v>
       </c>
       <c r="C55">
-        <v>6.885343637755983</v>
+        <v>6.756801470684393</v>
       </c>
       <c r="D55">
-        <v>8.878343637755982</v>
+        <v>8.890801470684393</v>
       </c>
       <c r="E55">
-        <v>1.223</v>
+        <v>1.364</v>
       </c>
       <c r="F55">
-        <v>7.473</v>
+        <v>7.614</v>
       </c>
       <c r="G55">
         <v>5.48</v>
@@ -5791,28 +5791,28 @@
         <v>2.21</v>
       </c>
       <c r="M55">
-        <v>0.4132569</v>
+        <v>0.4210542</v>
       </c>
       <c r="N55">
-        <v>1.7967431</v>
+        <v>1.7889458</v>
       </c>
       <c r="O55">
-        <v>0.48260519666</v>
+        <v>0.48051084188</v>
       </c>
       <c r="P55">
-        <v>1.31413790334</v>
+        <v>1.30843495812</v>
       </c>
       <c r="Q55">
-        <v>1.44413790334</v>
+        <v>1.43843495812</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1555681465879152</v>
+        <v>0.1576031606505985</v>
       </c>
       <c r="T55">
-        <v>2.13958548834227</v>
+        <v>2.179251700193651</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.347763098450383</v>
+        <v>5.24873044847908</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09433852069927533</v>
+        <v>0.09412340990223049</v>
       </c>
       <c r="C56">
-        <v>6.756801470684393</v>
+        <v>6.62829431367377</v>
       </c>
       <c r="D56">
-        <v>8.890801470684393</v>
+        <v>8.90329431367377</v>
       </c>
       <c r="E56">
-        <v>1.364</v>
+        <v>1.505000000000001</v>
       </c>
       <c r="F56">
-        <v>7.614</v>
+        <v>7.755000000000001</v>
       </c>
       <c r="G56">
         <v>5.48</v>
@@ -5873,28 +5873,28 @@
         <v>2.21</v>
       </c>
       <c r="M56">
-        <v>0.4210542</v>
+        <v>0.4288515000000001</v>
       </c>
       <c r="N56">
-        <v>1.7889458</v>
+        <v>1.7811485</v>
       </c>
       <c r="O56">
-        <v>0.48051084188</v>
+        <v>0.4784164871</v>
       </c>
       <c r="P56">
-        <v>1.30843495812</v>
+        <v>1.3027320129</v>
       </c>
       <c r="Q56">
-        <v>1.43843495812</v>
+        <v>1.4327320129</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1576031606505985</v>
+        <v>0.1597286197827344</v>
       </c>
       <c r="T56">
-        <v>2.179251700193651</v>
+        <v>2.220680854793982</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.24873044847908</v>
+        <v>5.153298985779459</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09412340990223049</v>
+        <v>0.09390829910518569</v>
       </c>
       <c r="C57">
-        <v>6.62829431367377</v>
+        <v>6.499822314514152</v>
       </c>
       <c r="D57">
-        <v>8.90329431367377</v>
+        <v>8.915822314514152</v>
       </c>
       <c r="E57">
-        <v>1.505000000000001</v>
+        <v>1.646000000000001</v>
       </c>
       <c r="F57">
-        <v>7.755000000000001</v>
+        <v>7.896000000000001</v>
       </c>
       <c r="G57">
         <v>5.48</v>
@@ -5955,28 +5955,28 @@
         <v>2.21</v>
       </c>
       <c r="M57">
-        <v>0.4288515000000001</v>
+        <v>0.4366488000000001</v>
       </c>
       <c r="N57">
-        <v>1.7811485</v>
+        <v>1.7733512</v>
       </c>
       <c r="O57">
-        <v>0.4784164871</v>
+        <v>0.47632213232</v>
       </c>
       <c r="P57">
-        <v>1.3027320129</v>
+        <v>1.29702906768</v>
       </c>
       <c r="Q57">
-        <v>1.4327320129</v>
+        <v>1.42702906768</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1597286197827344</v>
+        <v>0.1619506906936038</v>
       </c>
       <c r="T57">
-        <v>2.220680854793982</v>
+        <v>2.263993152785238</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.153298985779459</v>
+        <v>5.061275789604826</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09390829910518569</v>
+        <v>0.09369318830814086</v>
       </c>
       <c r="C58">
-        <v>6.499822314514152</v>
+        <v>6.371385621828585</v>
       </c>
       <c r="D58">
-        <v>8.915822314514152</v>
+        <v>8.928385621828586</v>
       </c>
       <c r="E58">
-        <v>1.646000000000001</v>
+        <v>1.787000000000001</v>
       </c>
       <c r="F58">
-        <v>7.896000000000001</v>
+        <v>8.037000000000001</v>
       </c>
       <c r="G58">
         <v>5.48</v>
@@ -6037,28 +6037,28 @@
         <v>2.21</v>
       </c>
       <c r="M58">
-        <v>0.4366488000000001</v>
+        <v>0.4444461000000001</v>
       </c>
       <c r="N58">
-        <v>1.7733512</v>
+        <v>1.7655539</v>
       </c>
       <c r="O58">
-        <v>0.47632213232</v>
+        <v>0.47422777754</v>
       </c>
       <c r="P58">
-        <v>1.29702906768</v>
+        <v>1.29132612246</v>
       </c>
       <c r="Q58">
-        <v>1.42702906768</v>
+        <v>1.42132612246</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1619506906936038</v>
+        <v>0.1642761137398625</v>
       </c>
       <c r="T58">
-        <v>2.263993152785238</v>
+        <v>2.309319976264459</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.061275789604826</v>
+        <v>4.972481477506496</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09369318830814086</v>
+        <v>0.09347807751109603</v>
       </c>
       <c r="C59">
-        <v>6.371385621828585</v>
+        <v>6.242984385078998</v>
       </c>
       <c r="D59">
-        <v>8.928385621828586</v>
+        <v>8.940984385078998</v>
       </c>
       <c r="E59">
-        <v>1.787000000000001</v>
+        <v>1.928000000000001</v>
       </c>
       <c r="F59">
-        <v>8.037000000000001</v>
+        <v>8.178000000000001</v>
       </c>
       <c r="G59">
         <v>5.48</v>
@@ -6119,28 +6119,28 @@
         <v>2.21</v>
       </c>
       <c r="M59">
-        <v>0.4444461000000001</v>
+        <v>0.4522434000000001</v>
       </c>
       <c r="N59">
-        <v>1.7655539</v>
+        <v>1.7577566</v>
       </c>
       <c r="O59">
-        <v>0.47422777754</v>
+        <v>0.47213342276</v>
       </c>
       <c r="P59">
-        <v>1.29132612246</v>
+        <v>1.28562317724</v>
       </c>
       <c r="Q59">
-        <v>1.42132612246</v>
+        <v>1.41562317724</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1642761137398625</v>
+        <v>0.1667122712168953</v>
       </c>
       <c r="T59">
-        <v>2.309319976264459</v>
+        <v>2.356805219909357</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.972481477506496</v>
+        <v>4.886749038239142</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09347807751109603</v>
+        <v>0.09326296671405122</v>
       </c>
       <c r="C60">
-        <v>6.242984385079</v>
+        <v>6.114618754572124</v>
       </c>
       <c r="D60">
-        <v>8.940984385078998</v>
+        <v>8.953618754572123</v>
       </c>
       <c r="E60">
-        <v>1.927999999999999</v>
+        <v>2.068999999999999</v>
       </c>
       <c r="F60">
-        <v>8.177999999999999</v>
+        <v>8.318999999999999</v>
       </c>
       <c r="G60">
         <v>5.48</v>
@@ -6201,28 +6201,28 @@
         <v>2.21</v>
       </c>
       <c r="M60">
-        <v>0.4522434</v>
+        <v>0.4600407</v>
       </c>
       <c r="N60">
-        <v>1.7577566</v>
+        <v>1.7499593</v>
       </c>
       <c r="O60">
-        <v>0.47213342276</v>
+        <v>0.47003906798</v>
       </c>
       <c r="P60">
-        <v>1.28562317724</v>
+        <v>1.27992023202</v>
       </c>
       <c r="Q60">
-        <v>1.41562317724</v>
+        <v>1.40992023202</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1667122712168953</v>
+        <v>0.1692672656440274</v>
       </c>
       <c r="T60">
-        <v>2.356805219909356</v>
+        <v>2.406606816902786</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.886749038239143</v>
+        <v>4.803922783353734</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09326296671405122</v>
+        <v>0.0930478559170064</v>
       </c>
       <c r="C61">
-        <v>6.114618754572124</v>
+        <v>5.986288881465489</v>
       </c>
       <c r="D61">
-        <v>8.953618754572123</v>
+        <v>8.966288881465488</v>
       </c>
       <c r="E61">
-        <v>2.068999999999999</v>
+        <v>2.209999999999999</v>
       </c>
       <c r="F61">
-        <v>8.318999999999999</v>
+        <v>8.459999999999999</v>
       </c>
       <c r="G61">
         <v>5.48</v>
@@ -6283,28 +6283,28 @@
         <v>2.21</v>
       </c>
       <c r="M61">
-        <v>0.4600407</v>
+        <v>0.467838</v>
       </c>
       <c r="N61">
-        <v>1.7499593</v>
+        <v>1.742162</v>
       </c>
       <c r="O61">
-        <v>0.47003906798</v>
+        <v>0.4679447132</v>
       </c>
       <c r="P61">
-        <v>1.27992023202</v>
+        <v>1.2742172868</v>
       </c>
       <c r="Q61">
-        <v>1.40992023202</v>
+        <v>1.4042172868</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1692672656440274</v>
+        <v>0.171950009792516</v>
       </c>
       <c r="T61">
-        <v>2.406606816902786</v>
+        <v>2.458898493745887</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.803922783353734</v>
+        <v>4.723857403631172</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0930478559170064</v>
+        <v>0.09283274511996156</v>
       </c>
       <c r="C62">
-        <v>5.986288881465489</v>
+        <v>5.857994917773432</v>
       </c>
       <c r="D62">
-        <v>8.966288881465488</v>
+        <v>8.978994917773431</v>
       </c>
       <c r="E62">
-        <v>2.209999999999999</v>
+        <v>2.350999999999999</v>
       </c>
       <c r="F62">
-        <v>8.459999999999999</v>
+        <v>8.600999999999999</v>
       </c>
       <c r="G62">
         <v>5.48</v>
@@ -6365,28 +6365,28 @@
         <v>2.21</v>
       </c>
       <c r="M62">
-        <v>0.467838</v>
+        <v>0.4756353</v>
       </c>
       <c r="N62">
-        <v>1.742162</v>
+        <v>1.7343647</v>
       </c>
       <c r="O62">
-        <v>0.4679447132</v>
+        <v>0.46585035842</v>
       </c>
       <c r="P62">
-        <v>1.2742172868</v>
+        <v>1.26851434158</v>
       </c>
       <c r="Q62">
-        <v>1.4042172868</v>
+        <v>1.39851434158</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.171950009792516</v>
+        <v>0.174770330564004</v>
       </c>
       <c r="T62">
-        <v>2.458898493745887</v>
+        <v>2.51387179504248</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.723857403631172</v>
+        <v>4.646417118325743</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09283274511996156</v>
+        <v>0.09261763432291674</v>
       </c>
       <c r="C63">
-        <v>5.857994917773432</v>
+        <v>5.729737016373186</v>
       </c>
       <c r="D63">
-        <v>8.978994917773431</v>
+        <v>8.991737016373184</v>
       </c>
       <c r="E63">
-        <v>2.350999999999999</v>
+        <v>2.491999999999999</v>
       </c>
       <c r="F63">
-        <v>8.600999999999999</v>
+        <v>8.741999999999999</v>
       </c>
       <c r="G63">
         <v>5.48</v>
@@ -6447,28 +6447,28 @@
         <v>2.21</v>
       </c>
       <c r="M63">
-        <v>0.4756353</v>
+        <v>0.4834326</v>
       </c>
       <c r="N63">
-        <v>1.7343647</v>
+        <v>1.7265674</v>
       </c>
       <c r="O63">
-        <v>0.46585035842</v>
+        <v>0.46375600364</v>
       </c>
       <c r="P63">
-        <v>1.26851434158</v>
+        <v>1.26281139636</v>
       </c>
       <c r="Q63">
-        <v>1.39851434158</v>
+        <v>1.39281139636</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.174770330564004</v>
+        <v>0.1777390892708335</v>
       </c>
       <c r="T63">
-        <v>2.51387179504248</v>
+        <v>2.571738427986263</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.646417118325743</v>
+        <v>4.571474906739843</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09261763432291674</v>
+        <v>0.09355447852587194</v>
       </c>
       <c r="C64">
-        <v>5.729737016373186</v>
+        <v>5.533505606161182</v>
       </c>
       <c r="D64">
-        <v>8.991737016373184</v>
+        <v>8.93650560616118</v>
       </c>
       <c r="E64">
-        <v>2.491999999999999</v>
+        <v>2.632999999999999</v>
       </c>
       <c r="F64">
-        <v>8.741999999999999</v>
+        <v>8.882999999999999</v>
       </c>
       <c r="G64">
         <v>5.48</v>
@@ -6529,45 +6529,45 @@
         <v>2.21</v>
       </c>
       <c r="M64">
-        <v>0.4834326</v>
+        <v>0.5134373999999999</v>
       </c>
       <c r="N64">
-        <v>1.7265674</v>
+        <v>1.6965626</v>
       </c>
       <c r="O64">
-        <v>0.46375600364</v>
+        <v>0.45569671436</v>
       </c>
       <c r="P64">
-        <v>1.26281139636</v>
+        <v>1.24086588564</v>
       </c>
       <c r="Q64">
-        <v>1.39281139636</v>
+        <v>1.37086588564</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1777390892708335</v>
+        <v>0.1808683214212755</v>
       </c>
       <c r="T64">
-        <v>2.571738427986263</v>
+        <v>2.632732987035115</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.2686</v>
       </c>
       <c r="W64">
-        <v>0.04044642</v>
+        <v>0.04227492000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.571474906739843</v>
+        <v>4.304322201693917</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09355447852587194</v>
+        <v>0.0933576527288271</v>
       </c>
       <c r="C65">
-        <v>5.533505606161182</v>
+        <v>5.404053046595445</v>
       </c>
       <c r="D65">
-        <v>8.93650560616118</v>
+        <v>8.948053046595444</v>
       </c>
       <c r="E65">
-        <v>2.632999999999999</v>
+        <v>2.773999999999999</v>
       </c>
       <c r="F65">
-        <v>8.882999999999999</v>
+        <v>9.023999999999999</v>
       </c>
       <c r="G65">
         <v>5.48</v>
@@ -6611,28 +6611,28 @@
         <v>2.21</v>
       </c>
       <c r="M65">
-        <v>0.5134373999999999</v>
+        <v>0.5215872</v>
       </c>
       <c r="N65">
-        <v>1.6965626</v>
+        <v>1.6884128</v>
       </c>
       <c r="O65">
-        <v>0.45569671436</v>
+        <v>0.45350767808</v>
       </c>
       <c r="P65">
-        <v>1.24086588564</v>
+        <v>1.23490512192</v>
       </c>
       <c r="Q65">
-        <v>1.37086588564</v>
+        <v>1.36490512192</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1808683214212755</v>
+        <v>0.1841713998022975</v>
       </c>
       <c r="T65">
-        <v>2.632732987035115</v>
+        <v>2.697116132697792</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.304322201693917</v>
+        <v>4.237067167292449</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0933576527288271</v>
+        <v>0.09316082693178229</v>
       </c>
       <c r="C66">
-        <v>5.404053046595445</v>
+        <v>5.274630368039363</v>
       </c>
       <c r="D66">
-        <v>8.948053046595444</v>
+        <v>8.959630368039363</v>
       </c>
       <c r="E66">
-        <v>2.773999999999999</v>
+        <v>2.915000000000001</v>
       </c>
       <c r="F66">
-        <v>9.023999999999999</v>
+        <v>9.165000000000001</v>
       </c>
       <c r="G66">
         <v>5.48</v>
@@ -6693,28 +6693,28 @@
         <v>2.21</v>
       </c>
       <c r="M66">
-        <v>0.5215872</v>
+        <v>0.5297370000000001</v>
       </c>
       <c r="N66">
-        <v>1.6884128</v>
+        <v>1.680263</v>
       </c>
       <c r="O66">
-        <v>0.45350767808</v>
+        <v>0.4513186418</v>
       </c>
       <c r="P66">
-        <v>1.23490512192</v>
+        <v>1.2289443582</v>
       </c>
       <c r="Q66">
-        <v>1.36490512192</v>
+        <v>1.3589443582</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1841713998022975</v>
+        <v>0.1876632255193779</v>
       </c>
       <c r="T66">
-        <v>2.697116132697792</v>
+        <v>2.765178315255479</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.237067167292449</v>
+        <v>4.171881518564872</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09316082693178229</v>
+        <v>0.09296400113473746</v>
       </c>
       <c r="C67">
-        <v>5.274630368039363</v>
+        <v>5.145237686626665</v>
       </c>
       <c r="D67">
-        <v>8.959630368039363</v>
+        <v>8.971237686626665</v>
       </c>
       <c r="E67">
-        <v>2.915000000000001</v>
+        <v>3.056000000000001</v>
       </c>
       <c r="F67">
-        <v>9.165000000000001</v>
+        <v>9.306000000000001</v>
       </c>
       <c r="G67">
         <v>5.48</v>
@@ -6775,28 +6775,28 @@
         <v>2.21</v>
       </c>
       <c r="M67">
-        <v>0.5297370000000001</v>
+        <v>0.5378868000000001</v>
       </c>
       <c r="N67">
-        <v>1.680263</v>
+        <v>1.6721132</v>
       </c>
       <c r="O67">
-        <v>0.4513186418</v>
+        <v>0.44912960552</v>
       </c>
       <c r="P67">
-        <v>1.2289443582</v>
+        <v>1.22298359448</v>
       </c>
       <c r="Q67">
-        <v>1.3589443582</v>
+        <v>1.35298359448</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1876632255193779</v>
+        <v>0.1913604527492278</v>
       </c>
       <c r="T67">
-        <v>2.765178315255479</v>
+        <v>2.837244155610677</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.171881518564872</v>
+        <v>4.10867119252601</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09296400113473746</v>
+        <v>0.09276717533769263</v>
       </c>
       <c r="C68">
-        <v>5.145237686626665</v>
+        <v>5.015875119093653</v>
       </c>
       <c r="D68">
-        <v>8.971237686626665</v>
+        <v>8.982875119093654</v>
       </c>
       <c r="E68">
-        <v>3.056000000000001</v>
+        <v>3.197000000000001</v>
       </c>
       <c r="F68">
-        <v>9.306000000000001</v>
+        <v>9.447000000000001</v>
       </c>
       <c r="G68">
         <v>5.48</v>
@@ -6857,28 +6857,28 @@
         <v>2.21</v>
       </c>
       <c r="M68">
-        <v>0.5378868000000001</v>
+        <v>0.5460366000000001</v>
       </c>
       <c r="N68">
-        <v>1.6721132</v>
+        <v>1.6639634</v>
       </c>
       <c r="O68">
-        <v>0.44912960552</v>
+        <v>0.44694056924</v>
       </c>
       <c r="P68">
-        <v>1.22298359448</v>
+        <v>1.21702283076</v>
       </c>
       <c r="Q68">
-        <v>1.35298359448</v>
+        <v>1.34702283076</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1913604527492278</v>
+        <v>0.1952817543566444</v>
       </c>
       <c r="T68">
-        <v>2.837244155610677</v>
+        <v>2.913677622654069</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.10867119252601</v>
+        <v>4.047347741891294</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09276717533769263</v>
+        <v>0.09431108154064782</v>
       </c>
       <c r="C69">
-        <v>5.015875119093653</v>
+        <v>4.784393084810535</v>
       </c>
       <c r="D69">
-        <v>8.982875119093654</v>
+        <v>8.892393084810536</v>
       </c>
       <c r="E69">
-        <v>3.197000000000001</v>
+        <v>3.338000000000001</v>
       </c>
       <c r="F69">
-        <v>9.447000000000001</v>
+        <v>9.588000000000001</v>
       </c>
       <c r="G69">
         <v>5.48</v>
@@ -6939,45 +6939,45 @@
         <v>2.21</v>
       </c>
       <c r="M69">
-        <v>0.5460366000000001</v>
+        <v>0.5877444000000001</v>
       </c>
       <c r="N69">
-        <v>1.6639634</v>
+        <v>1.6222556</v>
       </c>
       <c r="O69">
-        <v>0.44694056924</v>
+        <v>0.43573785416</v>
       </c>
       <c r="P69">
-        <v>1.21702283076</v>
+        <v>1.18651774584</v>
       </c>
       <c r="Q69">
-        <v>1.34702283076</v>
+        <v>1.31651774584</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1952817543566444</v>
+        <v>0.1994481373145244</v>
       </c>
       <c r="T69">
-        <v>2.913677622654069</v>
+        <v>2.994888181387673</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.2686</v>
       </c>
       <c r="W69">
-        <v>0.04227492000000001</v>
+        <v>0.04483482</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.047347741891294</v>
+        <v>3.760137910288894</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09431108154064782</v>
+        <v>0.09413985474360298</v>
       </c>
       <c r="C70">
-        <v>4.784393084810535</v>
+        <v>4.653338018578054</v>
       </c>
       <c r="D70">
-        <v>8.892393084810536</v>
+        <v>8.902338018578055</v>
       </c>
       <c r="E70">
-        <v>3.338000000000001</v>
+        <v>3.479000000000001</v>
       </c>
       <c r="F70">
-        <v>9.588000000000001</v>
+        <v>9.729000000000001</v>
       </c>
       <c r="G70">
         <v>5.48</v>
@@ -7021,28 +7021,28 @@
         <v>2.21</v>
       </c>
       <c r="M70">
-        <v>0.5877444000000001</v>
+        <v>0.5963877000000001</v>
       </c>
       <c r="N70">
-        <v>1.6222556</v>
+        <v>1.6136123</v>
       </c>
       <c r="O70">
-        <v>0.43573785416</v>
+        <v>0.4334162637799999</v>
       </c>
       <c r="P70">
-        <v>1.18651774584</v>
+        <v>1.18019603622</v>
       </c>
       <c r="Q70">
-        <v>1.31651774584</v>
+        <v>1.31019603622</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1994481373145244</v>
+        <v>0.2038833191729129</v>
       </c>
       <c r="T70">
-        <v>2.994888181387673</v>
+        <v>3.081338131007316</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.760137910288894</v>
+        <v>3.705643157965866</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09413985474360298</v>
+        <v>0.09396862794655816</v>
       </c>
       <c r="C71">
-        <v>4.653338018578054</v>
+        <v>4.522305221365544</v>
       </c>
       <c r="D71">
-        <v>8.902338018578055</v>
+        <v>8.912305221365544</v>
       </c>
       <c r="E71">
-        <v>3.479000000000001</v>
+        <v>3.620000000000001</v>
       </c>
       <c r="F71">
-        <v>9.729000000000001</v>
+        <v>9.870000000000001</v>
       </c>
       <c r="G71">
         <v>5.48</v>
@@ -7103,28 +7103,28 @@
         <v>2.21</v>
       </c>
       <c r="M71">
-        <v>0.5963877000000001</v>
+        <v>0.6050310000000001</v>
       </c>
       <c r="N71">
-        <v>1.6136123</v>
+        <v>1.604969</v>
       </c>
       <c r="O71">
-        <v>0.4334162637799999</v>
+        <v>0.4310946734</v>
       </c>
       <c r="P71">
-        <v>1.18019603622</v>
+        <v>1.1738743266</v>
       </c>
       <c r="Q71">
-        <v>1.31019603622</v>
+        <v>1.3038743266</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2038833191729129</v>
+        <v>0.2086141798218606</v>
       </c>
       <c r="T71">
-        <v>3.081338131007316</v>
+        <v>3.173551410601602</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.705643157965866</v>
+        <v>3.652705398566354</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09396862794655816</v>
+        <v>0.09379740114951333</v>
       </c>
       <c r="C72">
-        <v>4.522305221365544</v>
+        <v>4.391294768055118</v>
       </c>
       <c r="D72">
-        <v>8.912305221365544</v>
+        <v>8.922294768055119</v>
       </c>
       <c r="E72">
-        <v>3.620000000000001</v>
+        <v>3.761000000000001</v>
       </c>
       <c r="F72">
-        <v>9.870000000000001</v>
+        <v>10.011</v>
       </c>
       <c r="G72">
         <v>5.48</v>
@@ -7185,28 +7185,28 @@
         <v>2.21</v>
       </c>
       <c r="M72">
-        <v>0.6050310000000001</v>
+        <v>0.6136743000000001</v>
       </c>
       <c r="N72">
-        <v>1.604969</v>
+        <v>1.5963257</v>
       </c>
       <c r="O72">
-        <v>0.4310946734</v>
+        <v>0.42877308302</v>
       </c>
       <c r="P72">
-        <v>1.1738743266</v>
+        <v>1.16755261698</v>
       </c>
       <c r="Q72">
-        <v>1.3038743266</v>
+        <v>1.29755261698</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2086141798218606</v>
+        <v>0.2136713067224598</v>
       </c>
       <c r="T72">
-        <v>3.173551410601602</v>
+        <v>3.272124226719631</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.652705398566354</v>
+        <v>3.601258843656969</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09379740114951335</v>
+        <v>0.09362617435246851</v>
       </c>
       <c r="C73">
-        <v>4.391294768055118</v>
+        <v>4.260306733865002</v>
       </c>
       <c r="D73">
-        <v>8.922294768055117</v>
+        <v>8.932306733865001</v>
       </c>
       <c r="E73">
-        <v>3.760999999999999</v>
+        <v>3.901999999999999</v>
       </c>
       <c r="F73">
-        <v>10.011</v>
+        <v>10.152</v>
       </c>
       <c r="G73">
         <v>5.48</v>
@@ -7267,28 +7267,28 @@
         <v>2.21</v>
       </c>
       <c r="M73">
-        <v>0.6136743</v>
+        <v>0.6223175999999999</v>
       </c>
       <c r="N73">
-        <v>1.5963257</v>
+        <v>1.5876824</v>
       </c>
       <c r="O73">
-        <v>0.42877308302</v>
+        <v>0.42645149264</v>
       </c>
       <c r="P73">
-        <v>1.16755261698</v>
+        <v>1.16123090736</v>
       </c>
       <c r="Q73">
-        <v>1.29755261698</v>
+        <v>1.29123090736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2136713067224598</v>
+        <v>0.2190896569731018</v>
       </c>
       <c r="T73">
-        <v>3.27212422671963</v>
+        <v>3.377737958274662</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.601258843656969</v>
+        <v>3.551241359717289</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09362617435246851</v>
+        <v>0.0934549475554237</v>
       </c>
       <c r="C74">
-        <v>4.260306733865002</v>
+        <v>4.129341194351412</v>
       </c>
       <c r="D74">
-        <v>8.932306733865001</v>
+        <v>8.94234119435141</v>
       </c>
       <c r="E74">
-        <v>3.901999999999999</v>
+        <v>4.042999999999999</v>
       </c>
       <c r="F74">
-        <v>10.152</v>
+        <v>10.293</v>
       </c>
       <c r="G74">
         <v>5.48</v>
@@ -7349,28 +7349,28 @@
         <v>2.21</v>
       </c>
       <c r="M74">
-        <v>0.6223175999999999</v>
+        <v>0.6309608999999999</v>
       </c>
       <c r="N74">
-        <v>1.5876824</v>
+        <v>1.5790391</v>
       </c>
       <c r="O74">
-        <v>0.42645149264</v>
+        <v>0.42412990226</v>
       </c>
       <c r="P74">
-        <v>1.16123090736</v>
+        <v>1.15490919774</v>
       </c>
       <c r="Q74">
-        <v>1.29123090736</v>
+        <v>1.28490919774</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2190896569731018</v>
+        <v>0.2249093665015692</v>
       </c>
       <c r="T74">
-        <v>3.377737958274662</v>
+        <v>3.49117492920414</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.551241359717289</v>
+        <v>3.502594217803354</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0934549475554237</v>
+        <v>0.09479918155837887</v>
       </c>
       <c r="C75">
-        <v>4.129341194351412</v>
+        <v>3.910165562165943</v>
       </c>
       <c r="D75">
-        <v>8.94234119435141</v>
+        <v>8.864165562165942</v>
       </c>
       <c r="E75">
-        <v>4.042999999999999</v>
+        <v>4.183999999999999</v>
       </c>
       <c r="F75">
-        <v>10.293</v>
+        <v>10.434</v>
       </c>
       <c r="G75">
         <v>5.48</v>
@@ -7431,45 +7431,45 @@
         <v>2.21</v>
       </c>
       <c r="M75">
-        <v>0.6309608999999999</v>
+        <v>0.6688194</v>
       </c>
       <c r="N75">
-        <v>1.5790391</v>
+        <v>1.5411806</v>
       </c>
       <c r="O75">
-        <v>0.42412990226</v>
+        <v>0.4139611091600001</v>
       </c>
       <c r="P75">
-        <v>1.15490919774</v>
+        <v>1.12721949084</v>
       </c>
       <c r="Q75">
-        <v>1.28490919774</v>
+        <v>1.25721949084</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2249093665015692</v>
+        <v>0.2311767459937649</v>
       </c>
       <c r="T75">
-        <v>3.49117492920414</v>
+        <v>3.613337820974348</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.2686</v>
       </c>
       <c r="W75">
-        <v>0.04483482</v>
+        <v>0.04688274000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.502594217803354</v>
+        <v>3.304329988035634</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09479918155837887</v>
+        <v>0.09464843396133406</v>
       </c>
       <c r="C76">
-        <v>3.910165562165943</v>
+        <v>3.777864365848258</v>
       </c>
       <c r="D76">
-        <v>8.864165562165942</v>
+        <v>8.872864365848256</v>
       </c>
       <c r="E76">
-        <v>4.183999999999999</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="F76">
-        <v>10.434</v>
+        <v>10.575</v>
       </c>
       <c r="G76">
         <v>5.48</v>
@@ -7513,28 +7513,28 @@
         <v>2.21</v>
       </c>
       <c r="M76">
-        <v>0.6688194</v>
+        <v>0.6778575</v>
       </c>
       <c r="N76">
-        <v>1.5411806</v>
+        <v>1.5321425</v>
       </c>
       <c r="O76">
-        <v>0.4139611091600001</v>
+        <v>0.4115334755</v>
       </c>
       <c r="P76">
-        <v>1.12721949084</v>
+        <v>1.1206090245</v>
       </c>
       <c r="Q76">
-        <v>1.25721949084</v>
+        <v>1.2506090245</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2311767459937649</v>
+        <v>0.2379455158453362</v>
       </c>
       <c r="T76">
-        <v>3.613337820974348</v>
+        <v>3.745273744086173</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.304329988035634</v>
+        <v>3.260272254861825</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09464843396133406</v>
+        <v>0.09449768636428924</v>
       </c>
       <c r="C77">
-        <v>3.777864365848258</v>
+        <v>3.645580259354873</v>
       </c>
       <c r="D77">
-        <v>8.872864365848256</v>
+        <v>8.881580259354871</v>
       </c>
       <c r="E77">
-        <v>4.324999999999999</v>
+        <v>4.465999999999999</v>
       </c>
       <c r="F77">
-        <v>10.575</v>
+        <v>10.716</v>
       </c>
       <c r="G77">
         <v>5.48</v>
@@ -7595,28 +7595,28 @@
         <v>2.21</v>
       </c>
       <c r="M77">
-        <v>0.6778575</v>
+        <v>0.6868956000000001</v>
       </c>
       <c r="N77">
-        <v>1.5321425</v>
+        <v>1.5231044</v>
       </c>
       <c r="O77">
-        <v>0.4115334755</v>
+        <v>0.4091058418399999</v>
       </c>
       <c r="P77">
-        <v>1.1206090245</v>
+        <v>1.11399855816</v>
       </c>
       <c r="Q77">
-        <v>1.2506090245</v>
+        <v>1.24399855816</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2379455158453362</v>
+        <v>0.2452783498512051</v>
       </c>
       <c r="T77">
-        <v>3.745273744086173</v>
+        <v>3.888204327457315</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.260272254861825</v>
+        <v>3.217373935718907</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09449768636428924</v>
+        <v>0.0943469387672444</v>
       </c>
       <c r="C78">
-        <v>3.645580259354873</v>
+        <v>3.51331329309777</v>
       </c>
       <c r="D78">
-        <v>8.881580259354871</v>
+        <v>8.890313293097769</v>
       </c>
       <c r="E78">
-        <v>4.465999999999999</v>
+        <v>4.606999999999999</v>
       </c>
       <c r="F78">
-        <v>10.716</v>
+        <v>10.857</v>
       </c>
       <c r="G78">
         <v>5.48</v>
@@ -7677,28 +7677,28 @@
         <v>2.21</v>
       </c>
       <c r="M78">
-        <v>0.6868956000000001</v>
+        <v>0.6959337</v>
       </c>
       <c r="N78">
-        <v>1.5231044</v>
+        <v>1.5140663</v>
       </c>
       <c r="O78">
-        <v>0.4091058418399999</v>
+        <v>0.4066782081800001</v>
       </c>
       <c r="P78">
-        <v>1.11399855816</v>
+        <v>1.10738809182</v>
       </c>
       <c r="Q78">
-        <v>1.24399855816</v>
+        <v>1.23738809182</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2452783498512051</v>
+        <v>0.2532488215967148</v>
       </c>
       <c r="T78">
-        <v>3.888204327457315</v>
+        <v>4.043563657208558</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.217373935718907</v>
+        <v>3.175589858631648</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0943469387672444</v>
+        <v>0.09419619117019959</v>
       </c>
       <c r="C79">
-        <v>3.51331329309777</v>
+        <v>3.381063517687393</v>
       </c>
       <c r="D79">
-        <v>8.890313293097769</v>
+        <v>8.899063517687392</v>
       </c>
       <c r="E79">
-        <v>4.606999999999999</v>
+        <v>4.747999999999999</v>
       </c>
       <c r="F79">
-        <v>10.857</v>
+        <v>10.998</v>
       </c>
       <c r="G79">
         <v>5.48</v>
@@ -7759,28 +7759,28 @@
         <v>2.21</v>
       </c>
       <c r="M79">
-        <v>0.6959337</v>
+        <v>0.7049718</v>
       </c>
       <c r="N79">
-        <v>1.5140663</v>
+        <v>1.5050282</v>
       </c>
       <c r="O79">
-        <v>0.4066782081800001</v>
+        <v>0.40425057452</v>
       </c>
       <c r="P79">
-        <v>1.10738809182</v>
+        <v>1.10077762548</v>
       </c>
       <c r="Q79">
-        <v>1.23738809182</v>
+        <v>1.23077762548</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2532488215967148</v>
+        <v>0.2619438816827254</v>
       </c>
       <c r="T79">
-        <v>4.043563657208558</v>
+        <v>4.213046562391731</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.175589858631648</v>
+        <v>3.134877168136371</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09419619117019959</v>
+        <v>0.09404544357315475</v>
       </c>
       <c r="C80">
-        <v>3.381063517687393</v>
+        <v>3.248830983933646</v>
       </c>
       <c r="D80">
-        <v>8.899063517687392</v>
+        <v>8.907830983933644</v>
       </c>
       <c r="E80">
-        <v>4.747999999999999</v>
+        <v>4.888999999999999</v>
       </c>
       <c r="F80">
-        <v>10.998</v>
+        <v>11.139</v>
       </c>
       <c r="G80">
         <v>5.48</v>
@@ -7841,28 +7841,28 @@
         <v>2.21</v>
       </c>
       <c r="M80">
-        <v>0.7049718</v>
+        <v>0.7140099</v>
       </c>
       <c r="N80">
-        <v>1.5050282</v>
+        <v>1.4959901</v>
       </c>
       <c r="O80">
-        <v>0.40425057452</v>
+        <v>0.40182294086</v>
       </c>
       <c r="P80">
-        <v>1.10077762548</v>
+        <v>1.09416715914</v>
       </c>
       <c r="Q80">
-        <v>1.23077762548</v>
+        <v>1.22416715914</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2619438816827254</v>
+        <v>0.2714670427293084</v>
       </c>
       <c r="T80">
-        <v>4.213046562391731</v>
+        <v>4.398670696639969</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.134877168136371</v>
+        <v>3.09519517866629</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09404544357315475</v>
+        <v>0.09389469597610994</v>
       </c>
       <c r="C81">
-        <v>3.248830983933646</v>
+        <v>3.116615742846852</v>
       </c>
       <c r="D81">
-        <v>8.907830983933644</v>
+        <v>8.916615742846853</v>
       </c>
       <c r="E81">
-        <v>4.888999999999999</v>
+        <v>5.030000000000001</v>
       </c>
       <c r="F81">
-        <v>11.139</v>
+        <v>11.28</v>
       </c>
       <c r="G81">
         <v>5.48</v>
@@ -7923,28 +7923,28 @@
         <v>2.21</v>
       </c>
       <c r="M81">
-        <v>0.7140099</v>
+        <v>0.7230480000000001</v>
       </c>
       <c r="N81">
-        <v>1.4959901</v>
+        <v>1.486952</v>
       </c>
       <c r="O81">
-        <v>0.40182294086</v>
+        <v>0.3993953071999999</v>
       </c>
       <c r="P81">
-        <v>1.09416715914</v>
+        <v>1.0875566928</v>
       </c>
       <c r="Q81">
-        <v>1.22416715914</v>
+        <v>1.2175566928</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2714670427293084</v>
+        <v>0.2819425198805497</v>
       </c>
       <c r="T81">
-        <v>4.398670696639969</v>
+        <v>4.60285724431303</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.09519517866629</v>
+        <v>3.056505238932961</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09389469597610994</v>
+        <v>0.09374394837906511</v>
       </c>
       <c r="C82">
-        <v>3.116615742846852</v>
+        <v>2.984417845638767</v>
       </c>
       <c r="D82">
-        <v>8.916615742846853</v>
+        <v>8.925417845638767</v>
       </c>
       <c r="E82">
-        <v>5.030000000000001</v>
+        <v>5.171000000000001</v>
       </c>
       <c r="F82">
-        <v>11.28</v>
+        <v>11.421</v>
       </c>
       <c r="G82">
         <v>5.48</v>
@@ -8005,28 +8005,28 @@
         <v>2.21</v>
       </c>
       <c r="M82">
-        <v>0.7230480000000001</v>
+        <v>0.7320861000000001</v>
       </c>
       <c r="N82">
-        <v>1.486952</v>
+        <v>1.4779139</v>
       </c>
       <c r="O82">
-        <v>0.3993953071999999</v>
+        <v>0.39696767354</v>
       </c>
       <c r="P82">
-        <v>1.0875566928</v>
+        <v>1.08094622646</v>
       </c>
       <c r="Q82">
-        <v>1.2175566928</v>
+        <v>1.21094622646</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2819425198805497</v>
+        <v>0.2935206788371849</v>
       </c>
       <c r="T82">
-        <v>4.60285724431303</v>
+        <v>4.828537112793782</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.056505238932961</v>
+        <v>3.018770606353542</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09374394837906511</v>
+        <v>0.09827123518202029</v>
       </c>
       <c r="C83">
-        <v>2.984417845638767</v>
+        <v>2.586428932642431</v>
       </c>
       <c r="D83">
-        <v>8.925417845638767</v>
+        <v>8.668428932642431</v>
       </c>
       <c r="E83">
-        <v>5.171000000000001</v>
+        <v>5.312000000000001</v>
       </c>
       <c r="F83">
-        <v>11.421</v>
+        <v>11.562</v>
       </c>
       <c r="G83">
         <v>5.48</v>
@@ -8087,45 +8087,45 @@
         <v>2.21</v>
       </c>
       <c r="M83">
-        <v>0.7320861000000001</v>
+        <v>0.8313078000000002</v>
       </c>
       <c r="N83">
-        <v>1.4779139</v>
+        <v>1.3786922</v>
       </c>
       <c r="O83">
-        <v>0.39696767354</v>
+        <v>0.37031672492</v>
       </c>
       <c r="P83">
-        <v>1.08094622646</v>
+        <v>1.00837547508</v>
       </c>
       <c r="Q83">
-        <v>1.21094622646</v>
+        <v>1.13837547508</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2935206788371849</v>
+        <v>0.3063852999001128</v>
       </c>
       <c r="T83">
-        <v>4.828537112793782</v>
+        <v>5.07929252221684</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.2686</v>
       </c>
       <c r="W83">
-        <v>0.04688274000000001</v>
+        <v>0.05258766000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.018770606353542</v>
+        <v>2.658461763500835</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09827123518202029</v>
+        <v>0.09817753678497547</v>
       </c>
       <c r="C84">
-        <v>2.586428932642431</v>
+        <v>2.450597607987131</v>
       </c>
       <c r="D84">
-        <v>8.668428932642431</v>
+        <v>8.673597607987132</v>
       </c>
       <c r="E84">
-        <v>5.312000000000001</v>
+        <v>5.453000000000001</v>
       </c>
       <c r="F84">
-        <v>11.562</v>
+        <v>11.703</v>
       </c>
       <c r="G84">
         <v>5.48</v>
@@ -8169,28 +8169,28 @@
         <v>2.21</v>
       </c>
       <c r="M84">
-        <v>0.8313078000000002</v>
+        <v>0.8414457000000002</v>
       </c>
       <c r="N84">
-        <v>1.3786922</v>
+        <v>1.3685543</v>
       </c>
       <c r="O84">
-        <v>0.37031672492</v>
+        <v>0.3675936849799999</v>
       </c>
       <c r="P84">
-        <v>1.00837547508</v>
+        <v>1.00096061502</v>
       </c>
       <c r="Q84">
-        <v>1.13837547508</v>
+        <v>1.13096061502</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3063852999001128</v>
+        <v>0.3207634057939734</v>
       </c>
       <c r="T84">
-        <v>5.07929252221684</v>
+        <v>5.35954856804261</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.658461763500835</v>
+        <v>2.62643210369962</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09817753678497547</v>
+        <v>0.09808383838793064</v>
       </c>
       <c r="C85">
-        <v>2.450597607987131</v>
+        <v>2.314772450803206</v>
       </c>
       <c r="D85">
-        <v>8.673597607987132</v>
+        <v>8.678772450803207</v>
       </c>
       <c r="E85">
-        <v>5.453000000000001</v>
+        <v>5.594000000000001</v>
       </c>
       <c r="F85">
-        <v>11.703</v>
+        <v>11.844</v>
       </c>
       <c r="G85">
         <v>5.48</v>
@@ -8251,28 +8251,28 @@
         <v>2.21</v>
       </c>
       <c r="M85">
-        <v>0.8414457000000002</v>
+        <v>0.8515836000000001</v>
       </c>
       <c r="N85">
-        <v>1.3685543</v>
+        <v>1.3584164</v>
       </c>
       <c r="O85">
-        <v>0.3675936849799999</v>
+        <v>0.36487064504</v>
       </c>
       <c r="P85">
-        <v>1.00096061502</v>
+        <v>0.9935457549599999</v>
       </c>
       <c r="Q85">
-        <v>1.13096061502</v>
+        <v>1.12354575496</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3207634057939734</v>
+        <v>0.3369387749245666</v>
       </c>
       <c r="T85">
-        <v>5.35954856804261</v>
+        <v>5.674836619596603</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.62643210369962</v>
+        <v>2.595165054846054</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09808383838793067</v>
+        <v>0.09799013999088582</v>
       </c>
       <c r="C86">
-        <v>2.314772450803208</v>
+        <v>2.178953472136158</v>
       </c>
       <c r="D86">
-        <v>8.678772450803207</v>
+        <v>8.683953472136157</v>
       </c>
       <c r="E86">
-        <v>5.593999999999999</v>
+        <v>5.734999999999999</v>
       </c>
       <c r="F86">
-        <v>11.844</v>
+        <v>11.985</v>
       </c>
       <c r="G86">
         <v>5.48</v>
@@ -8333,28 +8333,28 @@
         <v>2.21</v>
       </c>
       <c r="M86">
-        <v>0.8515836</v>
+        <v>0.8617215</v>
       </c>
       <c r="N86">
-        <v>1.3584164</v>
+        <v>1.3482785</v>
       </c>
       <c r="O86">
-        <v>0.36487064504</v>
+        <v>0.3621476051</v>
       </c>
       <c r="P86">
-        <v>0.9935457549599999</v>
+        <v>0.9861308948999999</v>
       </c>
       <c r="Q86">
-        <v>1.12354575496</v>
+        <v>1.1161308949</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3369387749245665</v>
+        <v>0.3552708599392388</v>
       </c>
       <c r="T86">
-        <v>5.674836619596601</v>
+        <v>6.032163078024457</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.595165054846054</v>
+        <v>2.56463370125963</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09799013999088582</v>
+        <v>0.097896441593841</v>
       </c>
       <c r="C87">
-        <v>2.178953472136158</v>
+        <v>2.043140683057878</v>
       </c>
       <c r="D87">
-        <v>8.683953472136157</v>
+        <v>8.689140683057877</v>
       </c>
       <c r="E87">
-        <v>5.734999999999999</v>
+        <v>5.875999999999999</v>
       </c>
       <c r="F87">
-        <v>11.985</v>
+        <v>12.126</v>
       </c>
       <c r="G87">
         <v>5.48</v>
@@ -8415,28 +8415,28 @@
         <v>2.21</v>
       </c>
       <c r="M87">
-        <v>0.8617215</v>
+        <v>0.8718594000000001</v>
       </c>
       <c r="N87">
-        <v>1.3482785</v>
+        <v>1.3381406</v>
       </c>
       <c r="O87">
-        <v>0.3621476051</v>
+        <v>0.35942456516</v>
       </c>
       <c r="P87">
-        <v>0.9861308948999999</v>
+        <v>0.97871603484</v>
       </c>
       <c r="Q87">
-        <v>1.1161308949</v>
+        <v>1.10871603484</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3552708599392388</v>
+        <v>0.3762218142417214</v>
       </c>
       <c r="T87">
-        <v>6.032163078024457</v>
+        <v>6.44053617337058</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.56463370125963</v>
+        <v>2.534812379151959</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.097896441593841</v>
+        <v>0.09780274319679619</v>
       </c>
       <c r="C88">
-        <v>2.043140683057878</v>
+        <v>1.907334094666732</v>
       </c>
       <c r="D88">
-        <v>8.689140683057877</v>
+        <v>8.694334094666731</v>
       </c>
       <c r="E88">
-        <v>5.875999999999999</v>
+        <v>6.016999999999999</v>
       </c>
       <c r="F88">
-        <v>12.126</v>
+        <v>12.267</v>
       </c>
       <c r="G88">
         <v>5.48</v>
@@ -8497,28 +8497,28 @@
         <v>2.21</v>
       </c>
       <c r="M88">
-        <v>0.8718594000000001</v>
+        <v>0.8819973</v>
       </c>
       <c r="N88">
-        <v>1.3381406</v>
+        <v>1.3280027</v>
       </c>
       <c r="O88">
-        <v>0.35942456516</v>
+        <v>0.35670152522</v>
       </c>
       <c r="P88">
-        <v>0.97871603484</v>
+        <v>0.9713011747799999</v>
       </c>
       <c r="Q88">
-        <v>1.10871603484</v>
+        <v>1.10130117478</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3762218142417214</v>
+        <v>0.4003959922830475</v>
       </c>
       <c r="T88">
-        <v>6.44053617337058</v>
+        <v>6.911735898769951</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.534812379151959</v>
+        <v>2.505676604678948</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09780274319679619</v>
+        <v>0.1002192095997514</v>
       </c>
       <c r="C89">
-        <v>1.907334094666732</v>
+        <v>1.634351228786805</v>
       </c>
       <c r="D89">
-        <v>8.694334094666731</v>
+        <v>8.562351228786804</v>
       </c>
       <c r="E89">
-        <v>6.016999999999999</v>
+        <v>6.157999999999999</v>
       </c>
       <c r="F89">
-        <v>12.267</v>
+        <v>12.408</v>
       </c>
       <c r="G89">
         <v>5.48</v>
@@ -8579,45 +8579,45 @@
         <v>2.21</v>
       </c>
       <c r="M89">
-        <v>0.8819973</v>
+        <v>0.9405264</v>
       </c>
       <c r="N89">
-        <v>1.3280027</v>
+        <v>1.2694736</v>
       </c>
       <c r="O89">
-        <v>0.35670152522</v>
+        <v>0.34098060896</v>
       </c>
       <c r="P89">
-        <v>0.9713011747799999</v>
+        <v>0.9284929910399999</v>
       </c>
       <c r="Q89">
-        <v>1.10130117478</v>
+        <v>1.05849299104</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4003959922830475</v>
+        <v>0.4285991999979279</v>
       </c>
       <c r="T89">
-        <v>6.911735898769951</v>
+        <v>7.461468911735886</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.2686</v>
       </c>
       <c r="W89">
-        <v>0.05258766000000001</v>
+        <v>0.05544012000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.505676604678948</v>
+        <v>2.349747970923517</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1002192095997514</v>
+        <v>0.1001540358027065</v>
       </c>
       <c r="C90">
-        <v>1.634351228786805</v>
+        <v>1.496858298331656</v>
       </c>
       <c r="D90">
-        <v>8.562351228786804</v>
+        <v>8.565858298331655</v>
       </c>
       <c r="E90">
-        <v>6.157999999999999</v>
+        <v>6.298999999999999</v>
       </c>
       <c r="F90">
-        <v>12.408</v>
+        <v>12.549</v>
       </c>
       <c r="G90">
         <v>5.48</v>
@@ -8661,28 +8661,28 @@
         <v>2.21</v>
       </c>
       <c r="M90">
-        <v>0.9405264</v>
+        <v>0.9512142</v>
       </c>
       <c r="N90">
-        <v>1.2694736</v>
+        <v>1.2587858</v>
       </c>
       <c r="O90">
-        <v>0.34098060896</v>
+        <v>0.33810986588</v>
       </c>
       <c r="P90">
-        <v>0.9284929910399999</v>
+        <v>0.92067593412</v>
       </c>
       <c r="Q90">
-        <v>1.05849299104</v>
+        <v>1.05067593412</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4285991999979279</v>
+        <v>0.4619302636609685</v>
       </c>
       <c r="T90">
-        <v>7.461468911735886</v>
+        <v>8.111153381604717</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.349747970923517</v>
+        <v>2.323346308328871</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1001540358027065</v>
+        <v>0.1000888620056617</v>
       </c>
       <c r="C91">
-        <v>1.496858298331656</v>
+        <v>1.359368241988141</v>
       </c>
       <c r="D91">
-        <v>8.565858298331655</v>
+        <v>8.569368241988141</v>
       </c>
       <c r="E91">
-        <v>6.298999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="F91">
-        <v>12.549</v>
+        <v>12.69</v>
       </c>
       <c r="G91">
         <v>5.48</v>
@@ -8743,28 +8743,28 @@
         <v>2.21</v>
       </c>
       <c r="M91">
-        <v>0.9512142</v>
+        <v>0.961902</v>
       </c>
       <c r="N91">
-        <v>1.2587858</v>
+        <v>1.248098</v>
       </c>
       <c r="O91">
-        <v>0.33810986588</v>
+        <v>0.3352391228</v>
       </c>
       <c r="P91">
-        <v>0.92067593412</v>
+        <v>0.9128588771999999</v>
       </c>
       <c r="Q91">
-        <v>1.05067593412</v>
+        <v>1.0428588772</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4619302636609685</v>
+        <v>0.5019275400566171</v>
       </c>
       <c r="T91">
-        <v>8.111153381604717</v>
+        <v>8.890774745447315</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.323346308328871</v>
+        <v>2.297531349347438</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1000888620056617</v>
+        <v>0.1000236882086169</v>
       </c>
       <c r="C92">
-        <v>1.359368241988141</v>
+        <v>1.221881063290798</v>
       </c>
       <c r="D92">
-        <v>8.569368241988141</v>
+        <v>8.572881063290797</v>
       </c>
       <c r="E92">
-        <v>6.44</v>
+        <v>6.581</v>
       </c>
       <c r="F92">
-        <v>12.69</v>
+        <v>12.831</v>
       </c>
       <c r="G92">
         <v>5.48</v>
@@ -8825,28 +8825,28 @@
         <v>2.21</v>
       </c>
       <c r="M92">
-        <v>0.961902</v>
+        <v>0.9725898000000001</v>
       </c>
       <c r="N92">
-        <v>1.248098</v>
+        <v>1.2374102</v>
       </c>
       <c r="O92">
-        <v>0.3352391228</v>
+        <v>0.3323683797199999</v>
       </c>
       <c r="P92">
-        <v>0.9128588771999999</v>
+        <v>0.9050418202799999</v>
       </c>
       <c r="Q92">
-        <v>1.0428588772</v>
+        <v>1.03504182028</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5019275400566171</v>
+        <v>0.5508131000957432</v>
       </c>
       <c r="T92">
-        <v>8.890774745447315</v>
+        <v>9.843645301254936</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.297531349347438</v>
+        <v>2.272283752101862</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1000236882086169</v>
+        <v>0.09995851441157207</v>
       </c>
       <c r="C93">
-        <v>1.221881063290798</v>
+        <v>1.084396765779955</v>
       </c>
       <c r="D93">
-        <v>8.572881063290797</v>
+        <v>8.576396765779954</v>
       </c>
       <c r="E93">
-        <v>6.581</v>
+        <v>6.722</v>
       </c>
       <c r="F93">
-        <v>12.831</v>
+        <v>12.972</v>
       </c>
       <c r="G93">
         <v>5.48</v>
@@ -8907,28 +8907,28 @@
         <v>2.21</v>
       </c>
       <c r="M93">
-        <v>0.9725898000000001</v>
+        <v>0.9832776000000001</v>
       </c>
       <c r="N93">
-        <v>1.2374102</v>
+        <v>1.2267224</v>
       </c>
       <c r="O93">
-        <v>0.3323683797199999</v>
+        <v>0.32949763664</v>
       </c>
       <c r="P93">
-        <v>0.9050418202799999</v>
+        <v>0.8972247633599999</v>
       </c>
       <c r="Q93">
-        <v>1.03504182028</v>
+        <v>1.02722476336</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5508131000957432</v>
+        <v>0.611920050144651</v>
       </c>
       <c r="T93">
-        <v>9.843645301254936</v>
+        <v>11.03473349601446</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.272283752101862</v>
+        <v>2.247585015665972</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09995851441157207</v>
+        <v>0.09989334061452725</v>
       </c>
       <c r="C94">
-        <v>1.084396765779955</v>
+        <v>0.9469153530017529</v>
       </c>
       <c r="D94">
-        <v>8.576396765779954</v>
+        <v>8.579915353001752</v>
       </c>
       <c r="E94">
-        <v>6.722</v>
+        <v>6.863</v>
       </c>
       <c r="F94">
-        <v>12.972</v>
+        <v>13.113</v>
       </c>
       <c r="G94">
         <v>5.48</v>
@@ -8989,28 +8989,28 @@
         <v>2.21</v>
       </c>
       <c r="M94">
-        <v>0.9832776000000001</v>
+        <v>0.9939654</v>
       </c>
       <c r="N94">
-        <v>1.2267224</v>
+        <v>1.2160346</v>
       </c>
       <c r="O94">
-        <v>0.32949763664</v>
+        <v>0.32662689356</v>
       </c>
       <c r="P94">
-        <v>0.8972247633599999</v>
+        <v>0.8894077064399999</v>
       </c>
       <c r="Q94">
-        <v>1.02722476336</v>
+        <v>1.01940770644</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.611920050144651</v>
+        <v>0.690486128778961</v>
       </c>
       <c r="T94">
-        <v>11.03473349601446</v>
+        <v>12.56613260356242</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.247585015665972</v>
+        <v>2.22341743485236</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09989334061452725</v>
+        <v>0.09982816681748241</v>
       </c>
       <c r="C95">
-        <v>0.9469153530017529</v>
+        <v>0.8094368285081579</v>
       </c>
       <c r="D95">
-        <v>8.579915353001752</v>
+        <v>8.583436828508159</v>
       </c>
       <c r="E95">
-        <v>6.863</v>
+        <v>7.004000000000001</v>
       </c>
       <c r="F95">
-        <v>13.113</v>
+        <v>13.254</v>
       </c>
       <c r="G95">
         <v>5.48</v>
@@ -9071,28 +9071,28 @@
         <v>2.21</v>
       </c>
       <c r="M95">
-        <v>0.9939654</v>
+        <v>1.0046532</v>
       </c>
       <c r="N95">
-        <v>1.2160346</v>
+        <v>1.2053468</v>
       </c>
       <c r="O95">
-        <v>0.32662689356</v>
+        <v>0.3237561504799999</v>
       </c>
       <c r="P95">
-        <v>0.8894077064399999</v>
+        <v>0.8815906495199999</v>
       </c>
       <c r="Q95">
-        <v>1.01940770644</v>
+        <v>1.01159064952</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.690486128778961</v>
+        <v>0.7952409002913742</v>
       </c>
       <c r="T95">
-        <v>12.56613260356242</v>
+        <v>14.60799808029304</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.22341743485236</v>
+        <v>2.199764057885846</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09982816681748241</v>
+        <v>0.09976299302043759</v>
       </c>
       <c r="C96">
-        <v>0.8094368285081579</v>
+        <v>0.6719611958569676</v>
       </c>
       <c r="D96">
-        <v>8.583436828508159</v>
+        <v>8.586961195856968</v>
       </c>
       <c r="E96">
-        <v>7.004000000000001</v>
+        <v>7.145000000000001</v>
       </c>
       <c r="F96">
-        <v>13.254</v>
+        <v>13.395</v>
       </c>
       <c r="G96">
         <v>5.48</v>
@@ -9153,28 +9153,28 @@
         <v>2.21</v>
       </c>
       <c r="M96">
-        <v>1.0046532</v>
+        <v>1.015341</v>
       </c>
       <c r="N96">
-        <v>1.2053468</v>
+        <v>1.194659</v>
       </c>
       <c r="O96">
-        <v>0.3237561504799999</v>
+        <v>0.3208854073999999</v>
       </c>
       <c r="P96">
-        <v>0.8815906495199999</v>
+        <v>0.8737735925999998</v>
       </c>
       <c r="Q96">
-        <v>1.01159064952</v>
+        <v>1.0037735926</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7952409002913742</v>
+        <v>0.9418975804087529</v>
       </c>
       <c r="T96">
-        <v>14.60799808029304</v>
+        <v>17.46660974771591</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.199764057885846</v>
+        <v>2.176608646750204</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09976299302043759</v>
+        <v>0.09969781922339277</v>
       </c>
       <c r="C97">
-        <v>0.6719611958569676</v>
+        <v>0.5344884586118237</v>
       </c>
       <c r="D97">
-        <v>8.586961195856968</v>
+        <v>8.590488458611825</v>
       </c>
       <c r="E97">
-        <v>7.145000000000001</v>
+        <v>7.286000000000001</v>
       </c>
       <c r="F97">
-        <v>13.395</v>
+        <v>13.536</v>
       </c>
       <c r="G97">
         <v>5.48</v>
@@ -9235,28 +9235,28 @@
         <v>2.21</v>
       </c>
       <c r="M97">
-        <v>1.015341</v>
+        <v>1.0260288</v>
       </c>
       <c r="N97">
-        <v>1.194659</v>
+        <v>1.1839712</v>
       </c>
       <c r="O97">
-        <v>0.3208854073999999</v>
+        <v>0.31801466432</v>
       </c>
       <c r="P97">
-        <v>0.8737735925999998</v>
+        <v>0.8659565356799999</v>
       </c>
       <c r="Q97">
-        <v>1.0037735926</v>
+        <v>0.9959565356799998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9418975804087529</v>
+        <v>1.161882600584821</v>
       </c>
       <c r="T97">
-        <v>17.46660974771591</v>
+        <v>21.75452724885021</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.176608646750204</v>
+        <v>2.153935640013223</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09969781922339277</v>
+        <v>0.09963264542634796</v>
       </c>
       <c r="C98">
-        <v>0.5344884586118255</v>
+        <v>0.3970186203422266</v>
       </c>
       <c r="D98">
-        <v>8.590488458611825</v>
+        <v>8.594018620342226</v>
       </c>
       <c r="E98">
-        <v>7.286</v>
+        <v>7.427</v>
       </c>
       <c r="F98">
-        <v>13.536</v>
+        <v>13.677</v>
       </c>
       <c r="G98">
         <v>5.48</v>
@@ -9317,28 +9317,28 @@
         <v>2.21</v>
       </c>
       <c r="M98">
-        <v>1.0260288</v>
+        <v>1.0367166</v>
       </c>
       <c r="N98">
-        <v>1.1839712</v>
+        <v>1.1732834</v>
       </c>
       <c r="O98">
-        <v>0.31801466432</v>
+        <v>0.31514392124</v>
       </c>
       <c r="P98">
-        <v>0.86595653568</v>
+        <v>0.8581394787599999</v>
       </c>
       <c r="Q98">
-        <v>0.9959565356799999</v>
+        <v>0.9881394787599997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.161882600584818</v>
+        <v>1.528524300878264</v>
       </c>
       <c r="T98">
-        <v>21.75452724885015</v>
+        <v>28.90105641740729</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.153935640013224</v>
+        <v>2.131730117951232</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09963264542634796</v>
+        <v>0.09956747162930313</v>
       </c>
       <c r="C99">
-        <v>0.3970186203422266</v>
+        <v>0.2595516846235491</v>
       </c>
       <c r="D99">
-        <v>8.594018620342226</v>
+        <v>8.597551684623548</v>
       </c>
       <c r="E99">
-        <v>7.427</v>
+        <v>7.568</v>
       </c>
       <c r="F99">
-        <v>13.677</v>
+        <v>13.818</v>
       </c>
       <c r="G99">
         <v>5.48</v>
@@ -9399,28 +9399,28 @@
         <v>2.21</v>
       </c>
       <c r="M99">
-        <v>1.0367166</v>
+        <v>1.0474044</v>
       </c>
       <c r="N99">
-        <v>1.1732834</v>
+        <v>1.1625956</v>
       </c>
       <c r="O99">
-        <v>0.31514392124</v>
+        <v>0.31227317816</v>
       </c>
       <c r="P99">
-        <v>0.8581394787599999</v>
+        <v>0.85032242184</v>
       </c>
       <c r="Q99">
-        <v>0.9881394787599997</v>
+        <v>0.9803224218399998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.528524300878264</v>
+        <v>2.261807701465154</v>
       </c>
       <c r="T99">
-        <v>28.90105641740729</v>
+        <v>43.19411475452156</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.131730117951232</v>
+        <v>2.109977769808872</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09956747162930313</v>
+        <v>0.09950229783225831</v>
       </c>
       <c r="C100">
-        <v>0.2595516846235491</v>
+        <v>0.1220876550370402</v>
       </c>
       <c r="D100">
-        <v>8.597551684623548</v>
+        <v>8.601087655037039</v>
       </c>
       <c r="E100">
-        <v>7.568</v>
+        <v>7.709</v>
       </c>
       <c r="F100">
-        <v>13.818</v>
+        <v>13.959</v>
       </c>
       <c r="G100">
         <v>5.48</v>
@@ -9481,28 +9481,28 @@
         <v>2.21</v>
       </c>
       <c r="M100">
-        <v>1.0474044</v>
+        <v>1.0580922</v>
       </c>
       <c r="N100">
-        <v>1.1625956</v>
+        <v>1.1519078</v>
       </c>
       <c r="O100">
-        <v>0.31227317816</v>
+        <v>0.30940243508</v>
       </c>
       <c r="P100">
-        <v>0.85032242184</v>
+        <v>0.8425053649199998</v>
       </c>
       <c r="Q100">
-        <v>0.9803224218399998</v>
+        <v>0.9725053649199997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.261807701465154</v>
+        <v>4.461657903225825</v>
       </c>
       <c r="T100">
-        <v>43.19411475452156</v>
+        <v>86.07328976586436</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.109977769808872</v>
+        <v>2.088664863043125</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09950229783225831</v>
-      </c>
-      <c r="C101">
-        <v>0.1220876550370402</v>
-      </c>
-      <c r="D101">
-        <v>8.601087655037039</v>
-      </c>
-      <c r="E101">
-        <v>7.709</v>
-      </c>
-      <c r="F101">
-        <v>13.959</v>
-      </c>
-      <c r="G101">
-        <v>5.48</v>
-      </c>
-      <c r="H101">
-        <v>7.85</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.34</v>
-      </c>
-      <c r="K101">
-        <v>0.1299999999999999</v>
-      </c>
-      <c r="L101">
-        <v>2.21</v>
-      </c>
-      <c r="M101">
-        <v>1.0580922</v>
-      </c>
-      <c r="N101">
-        <v>1.1519078</v>
-      </c>
-      <c r="O101">
-        <v>0.30940243508</v>
-      </c>
-      <c r="P101">
-        <v>0.8425053649199998</v>
-      </c>
-      <c r="Q101">
-        <v>0.9725053649199997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.461657903225825</v>
-      </c>
-      <c r="T101">
-        <v>86.07328976586436</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2686</v>
-      </c>
-      <c r="W101">
-        <v>0.05544012000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.088664863043125</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
